--- a/maestra.xlsx
+++ b/maestra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\cotizador-web-mp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AE3276-2131-49A9-ACC0-DECAEA03CC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9000A0CA-3498-4E16-AEED-871BD437A169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{192F143D-BAEC-4662-86EC-0FD2BF508275}"/>
   </bookViews>
@@ -915,28 +915,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Crédito Hipotecario</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">* </t>
     </r>
     <r>
@@ -996,6 +974,9 @@
   </si>
   <si>
     <t>Aporte inmobiliaria en UF:</t>
+  </si>
+  <si>
+    <t>* Crédito Hipotecario</t>
   </si>
 </sst>
 </file>
@@ -1277,7 +1258,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1350,8 +1331,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1532,32 +1519,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1565,12 +1526,9 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1631,9 +1589,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1641,9 +1596,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1755,21 +1707,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
@@ -1779,9 +1719,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1827,12 +1764,8 @@
     <xf numFmtId="9" fontId="10" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="3"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1840,22 +1773,11 @@
     <xf numFmtId="166" fontId="26" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="10" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1893,10 +1815,6 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1960,6 +1878,65 @@
     <xf numFmtId="167" fontId="35" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="35" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency [0]" xfId="1" builtinId="7"/>
@@ -66506,10 +66483,10 @@
     <dataField name="Precio de Lista" fld="13" subtotal="min" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="3">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -66864,1243 +66841,1243 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
+      <c r="Q2" s="141"/>
+      <c r="R2" s="141"/>
+      <c r="S2" s="141"/>
+      <c r="T2" s="141"/>
+      <c r="U2" s="141"/>
+      <c r="V2" s="141"/>
+      <c r="W2" s="141"/>
     </row>
     <row r="3" spans="1:29" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="14"/>
-      <c r="AA3" s="16" t="s">
+      <c r="P3" s="10"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="13"/>
+      <c r="AA3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="AB3" s="16" t="s">
+      <c r="AB3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="AC3" s="16" t="s">
+      <c r="AC3" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="18">
         <v>2028</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="20">
         <v>0.1</v>
       </c>
-      <c r="F4" s="22"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="21">
+      <c r="F4" s="21"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="20">
         <v>0.02</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="23">
         <f t="shared" ref="I4:I8" si="0">20%-L4-H4</f>
         <v>0.08</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="24">
         <v>21</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="24">
+      <c r="L4" s="23">
         <v>0.1</v>
       </c>
-      <c r="M4" s="25" t="s">
+      <c r="M4" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="27" t="s">
+      <c r="P4" s="25"/>
+      <c r="Q4" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="R4" s="27"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="27" t="s">
+      <c r="R4" s="137"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="W4" s="27"/>
-      <c r="X4" s="31"/>
-      <c r="AA4" s="32" t="s">
+      <c r="W4" s="137"/>
+      <c r="X4" s="142"/>
+      <c r="AA4" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="AB4" s="32" t="s">
+      <c r="AB4" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="AC4" s="32" t="s">
+      <c r="AC4" s="29" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="18">
         <v>2029</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="20">
         <v>0.1</v>
       </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="21">
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="20">
         <v>0.02</v>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="23">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="24">
         <v>34</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="24">
+      <c r="L5" s="23">
         <v>0.1</v>
       </c>
-      <c r="M5" s="25" t="s">
+      <c r="M5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="33"/>
-      <c r="S5" s="34"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="26"/>
-      <c r="X5" s="35"/>
-      <c r="AA5" s="32" t="s">
+      <c r="P5" s="25"/>
+      <c r="Q5" s="30"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="25"/>
+      <c r="X5" s="32"/>
+      <c r="AA5" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="AB5" s="32" t="s">
+      <c r="AB5" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="AC5" s="32" t="s">
+      <c r="AC5" s="29" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="18">
         <v>2029</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>0.1</v>
       </c>
-      <c r="F6" s="36"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24">
+      <c r="F6" s="33"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="23">
         <v>0.02</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="23">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="J6" s="37">
+      <c r="J6" s="34">
         <v>21</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="24">
+      <c r="L6" s="23">
         <v>0.1</v>
       </c>
-      <c r="M6" s="37" t="s">
+      <c r="M6" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="33">
+      <c r="P6" s="25"/>
+      <c r="Q6" s="30">
         <v>1</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="S6" s="34"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="26"/>
-      <c r="V6" s="33">
+      <c r="S6" s="31"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="30">
         <v>1</v>
       </c>
       <c r="W6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="X6" s="35"/>
-      <c r="AA6" s="32" t="s">
+      <c r="X6" s="32"/>
+      <c r="AA6" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="AB6" s="32" t="s">
+      <c r="AB6" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="AC6" s="32" t="s">
+      <c r="AC6" s="29" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="18">
         <v>2029</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="35">
         <v>0.15</v>
       </c>
-      <c r="F7" s="36"/>
-      <c r="G7" s="23">
+      <c r="F7" s="33"/>
+      <c r="G7" s="22">
         <v>500000</v>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="35">
         <v>0.01</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="23">
         <f t="shared" si="0"/>
         <v>9.0000000000000011E-2</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="24">
         <v>35</v>
       </c>
-      <c r="K7" s="24" t="s">
+      <c r="K7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="23">
         <v>0.1</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="33">
+      <c r="P7" s="25"/>
+      <c r="Q7" s="30">
         <v>2</v>
       </c>
-      <c r="R7" s="39" t="s">
+      <c r="R7" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="S7" s="34"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="26"/>
-      <c r="V7" s="33">
+      <c r="S7" s="31"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="30">
         <v>2</v>
       </c>
       <c r="W7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="X7" s="35"/>
-      <c r="AA7" s="32" t="s">
+      <c r="X7" s="32"/>
+      <c r="AA7" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="AB7" s="32" t="s">
+      <c r="AB7" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="AC7" s="32" t="s">
+      <c r="AC7" s="29" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="18">
         <v>2029</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <v>0.1</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="40"/>
-      <c r="H8" s="21">
+      <c r="G8" s="37"/>
+      <c r="H8" s="20">
         <v>0.02</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="20">
         <f t="shared" si="0"/>
         <v>0.08</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="24">
         <v>34</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="K8" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="20">
         <v>0.1</v>
       </c>
-      <c r="M8" s="25" t="s">
+      <c r="M8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="33">
+      <c r="P8" s="25"/>
+      <c r="Q8" s="30">
         <v>3</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="S8" s="34"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="26"/>
-      <c r="V8" s="33">
+      <c r="S8" s="31"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="30">
         <v>3</v>
       </c>
-      <c r="W8" s="39" t="s">
+      <c r="W8" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="X8" s="35"/>
-      <c r="AA8" s="32" t="s">
+      <c r="X8" s="32"/>
+      <c r="AA8" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="AB8" s="32" t="s">
+      <c r="AB8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="AC8" s="32" t="s">
+      <c r="AC8" s="29" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18" t="s">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="18">
         <v>2029</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="35">
         <v>0.15</v>
       </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="40">
+      <c r="F9" s="21"/>
+      <c r="G9" s="37">
         <v>500000</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="35">
         <v>0.01</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="20">
         <f>20%-L9-H9</f>
         <v>9.0000000000000011E-2</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="24">
         <v>36</v>
       </c>
-      <c r="K9" s="21" t="s">
+      <c r="K9" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="20">
         <v>0.1</v>
       </c>
-      <c r="M9" s="25" t="s">
+      <c r="M9" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="33">
+      <c r="P9" s="25"/>
+      <c r="Q9" s="30">
         <v>4</v>
       </c>
       <c r="R9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="S9" s="34"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="26"/>
-      <c r="V9" s="33">
+      <c r="S9" s="31"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="30">
         <v>4</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="X9" s="35"/>
-      <c r="AA9" s="32" t="s">
+      <c r="X9" s="32"/>
+      <c r="AA9" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="AB9" s="32" t="s">
+      <c r="AB9" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="AC9" s="32" t="s">
+      <c r="AC9" s="29" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="41"/>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="38"/>
+      <c r="B10" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="41">
         <v>0.1</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="46" t="s">
+      <c r="G10" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44">
+      <c r="H10" s="41"/>
+      <c r="I10" s="41">
         <v>0.1</v>
       </c>
-      <c r="J10" s="47">
+      <c r="J10" s="44">
         <v>60</v>
       </c>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44">
+      <c r="K10" s="41"/>
+      <c r="L10" s="41">
         <v>0.1</v>
       </c>
-      <c r="M10" s="45" t="s">
+      <c r="M10" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="33">
+      <c r="P10" s="25"/>
+      <c r="Q10" s="30">
         <v>5</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="S10" s="48"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="33">
+      <c r="S10" s="45"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="30">
         <v>5</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="X10" s="35"/>
-      <c r="AA10" s="32" t="s">
+      <c r="X10" s="32"/>
+      <c r="AA10" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="AB10" s="32" t="s">
+      <c r="AB10" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="AC10" s="32" t="s">
+      <c r="AC10" s="29" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="17"/>
-      <c r="B11" s="49" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="48">
         <v>0.13</v>
       </c>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52" t="s">
+      <c r="F11" s="49"/>
+      <c r="G11" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53">
+      <c r="H11" s="50"/>
+      <c r="I11" s="50">
         <v>0.1</v>
       </c>
-      <c r="J11" s="54">
+      <c r="J11" s="51">
         <v>60</v>
       </c>
-      <c r="K11" s="53"/>
-      <c r="L11" s="55">
+      <c r="K11" s="50"/>
+      <c r="L11" s="52">
         <v>0.15</v>
       </c>
-      <c r="M11" s="56" t="s">
+      <c r="M11" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="33">
+      <c r="P11" s="25"/>
+      <c r="Q11" s="30">
         <v>6</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="S11" s="48"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="33">
+      <c r="S11" s="45"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="30">
         <v>6</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="X11" s="35"/>
-      <c r="AA11" s="32" t="s">
+      <c r="X11" s="32"/>
+      <c r="AA11" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="AB11" s="32" t="s">
+      <c r="AB11" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="AC11" s="32" t="s">
+      <c r="AC11" s="29" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="57">
+      <c r="E12" s="54">
         <v>0.1</v>
       </c>
-      <c r="F12" s="58"/>
-      <c r="G12" s="59" t="s">
+      <c r="F12" s="55"/>
+      <c r="G12" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="60"/>
-      <c r="I12" s="61">
+      <c r="H12" s="57"/>
+      <c r="I12" s="58">
         <v>0.1</v>
       </c>
-      <c r="J12" s="60">
+      <c r="J12" s="57">
         <v>60</v>
       </c>
-      <c r="K12" s="60"/>
-      <c r="L12" s="61">
+      <c r="K12" s="57"/>
+      <c r="L12" s="58">
         <v>0.1</v>
       </c>
-      <c r="M12" s="60" t="s">
+      <c r="M12" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="33">
+      <c r="P12" s="25"/>
+      <c r="Q12" s="30">
         <v>7</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="S12" s="48"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="33">
+      <c r="S12" s="45"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="30">
         <v>7</v>
       </c>
-      <c r="W12" s="39" t="s">
+      <c r="W12" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="X12" s="35"/>
-      <c r="AA12" s="32" t="s">
+      <c r="X12" s="32"/>
+      <c r="AA12" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="AB12" s="32" t="s">
+      <c r="AB12" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="AC12" s="32" t="s">
+      <c r="AC12" s="29" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="62">
+      <c r="E13" s="59">
         <v>0.13</v>
       </c>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59" t="s">
+      <c r="F13" s="56"/>
+      <c r="G13" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="60"/>
-      <c r="I13" s="61">
+      <c r="H13" s="57"/>
+      <c r="I13" s="58">
         <v>0.1</v>
       </c>
-      <c r="J13" s="60">
+      <c r="J13" s="57">
         <v>60</v>
       </c>
-      <c r="K13" s="60"/>
-      <c r="L13" s="61">
+      <c r="K13" s="57"/>
+      <c r="L13" s="58">
         <v>0.1</v>
       </c>
-      <c r="M13" s="60" t="s">
+      <c r="M13" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="P13" s="26"/>
-      <c r="Q13" s="33">
+      <c r="P13" s="25"/>
+      <c r="Q13" s="30">
         <v>8</v>
       </c>
-      <c r="R13" s="39" t="s">
+      <c r="R13" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="S13" s="34"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="26"/>
-      <c r="V13" s="33">
+      <c r="S13" s="31"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="30">
         <v>8</v>
       </c>
-      <c r="W13" s="39" t="s">
+      <c r="W13" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="X13" s="35"/>
-      <c r="AA13" s="32" t="s">
+      <c r="X13" s="32"/>
+      <c r="AA13" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="AB13" s="32" t="s">
+      <c r="AB13" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="AC13" s="32" t="s">
+      <c r="AC13" s="29" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="57">
+      <c r="E14" s="54">
         <v>0.1</v>
       </c>
-      <c r="F14" s="58" t="s">
+      <c r="F14" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="G14" s="59" t="s">
+      <c r="G14" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="60"/>
-      <c r="I14" s="61">
+      <c r="H14" s="57"/>
+      <c r="I14" s="58">
         <v>0.1</v>
       </c>
-      <c r="J14" s="60">
+      <c r="J14" s="57">
         <v>60</v>
       </c>
-      <c r="K14" s="60"/>
-      <c r="L14" s="61">
+      <c r="K14" s="57"/>
+      <c r="L14" s="58">
         <v>0.1</v>
       </c>
-      <c r="M14" s="60" t="s">
+      <c r="M14" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="33">
+      <c r="P14" s="25"/>
+      <c r="Q14" s="30">
         <v>9</v>
       </c>
-      <c r="R14" s="39" t="s">
+      <c r="R14" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="S14" s="34"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="26"/>
-      <c r="V14" s="33">
+      <c r="S14" s="31"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="30">
         <v>9</v>
       </c>
-      <c r="W14" s="39" t="s">
+      <c r="W14" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="X14" s="35"/>
-      <c r="AA14" s="32" t="s">
+      <c r="X14" s="32"/>
+      <c r="AA14" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="AB14" s="32" t="s">
+      <c r="AB14" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="AC14" s="32" t="s">
+      <c r="AC14" s="29" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="62">
+      <c r="E15" s="59">
         <v>0.13</v>
       </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="58" t="s">
+      <c r="F15" s="56"/>
+      <c r="G15" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="60"/>
-      <c r="I15" s="61">
+      <c r="H15" s="57"/>
+      <c r="I15" s="58">
         <v>0.1</v>
       </c>
-      <c r="J15" s="60">
+      <c r="J15" s="57">
         <v>60</v>
       </c>
-      <c r="K15" s="60"/>
-      <c r="L15" s="61">
+      <c r="K15" s="57"/>
+      <c r="L15" s="58">
         <v>0.1</v>
       </c>
-      <c r="M15" s="60" t="s">
+      <c r="M15" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="33">
+      <c r="P15" s="25"/>
+      <c r="Q15" s="30">
         <v>10</v>
       </c>
-      <c r="R15" s="39" t="s">
+      <c r="R15" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="S15" s="34"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="26"/>
-      <c r="V15" s="33">
+      <c r="S15" s="31"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="30">
         <v>10</v>
       </c>
-      <c r="W15" s="39" t="s">
+      <c r="W15" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="X15" s="35"/>
-      <c r="AA15" s="32" t="s">
+      <c r="X15" s="32"/>
+      <c r="AA15" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="AB15" s="32" t="s">
+      <c r="AB15" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="AC15" s="32" t="s">
+      <c r="AC15" s="29" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A16" s="41"/>
-      <c r="B16" s="18" t="s">
+      <c r="A16" s="38"/>
+      <c r="B16" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E16" s="57">
+      <c r="E16" s="54">
         <v>0.1</v>
       </c>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58" t="s">
+      <c r="F16" s="55"/>
+      <c r="G16" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="H16" s="60"/>
-      <c r="I16" s="61">
+      <c r="H16" s="57"/>
+      <c r="I16" s="58">
         <v>0.1</v>
       </c>
-      <c r="J16" s="60">
+      <c r="J16" s="57">
         <v>60</v>
       </c>
-      <c r="K16" s="60"/>
-      <c r="L16" s="61">
+      <c r="K16" s="57"/>
+      <c r="L16" s="58">
         <v>0.1</v>
       </c>
-      <c r="M16" s="60" t="s">
+      <c r="M16" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="33">
+      <c r="P16" s="25"/>
+      <c r="Q16" s="30">
         <v>11</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="S16" s="34"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="26"/>
-      <c r="V16" s="33">
+      <c r="S16" s="31"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="30">
         <v>11</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="X16" s="35"/>
-      <c r="AA16" s="32" t="s">
+      <c r="X16" s="32"/>
+      <c r="AA16" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="AB16" s="32" t="s">
+      <c r="AB16" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="AC16" s="32" t="s">
+      <c r="AC16" s="29" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A17" s="41"/>
-      <c r="B17" s="63" t="s">
+      <c r="A17" s="38"/>
+      <c r="B17" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E17" s="57">
+      <c r="E17" s="54">
         <v>0.1</v>
       </c>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58" t="s">
+      <c r="F17" s="55"/>
+      <c r="G17" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="60"/>
-      <c r="I17" s="61">
+      <c r="H17" s="57"/>
+      <c r="I17" s="58">
         <v>0.1</v>
       </c>
-      <c r="J17" s="60">
+      <c r="J17" s="57">
         <v>60</v>
       </c>
-      <c r="K17" s="60"/>
-      <c r="L17" s="61">
+      <c r="K17" s="57"/>
+      <c r="L17" s="58">
         <v>0.1</v>
       </c>
-      <c r="M17" s="60" t="s">
+      <c r="M17" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="33">
+      <c r="P17" s="25"/>
+      <c r="Q17" s="30">
         <v>12</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="S17" s="34"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="26"/>
-      <c r="V17" s="33">
+      <c r="S17" s="31"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="30">
         <v>12</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="X17" s="35"/>
-      <c r="AA17" s="32" t="s">
+      <c r="X17" s="32"/>
+      <c r="AA17" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AB17" s="32" t="s">
+      <c r="AB17" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="AC17" s="32" t="s">
+      <c r="AC17" s="29" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="64" t="s">
+      <c r="C18" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="64" t="s">
+      <c r="D18" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="61">
+      <c r="E18" s="58">
         <v>0.1</v>
       </c>
-      <c r="F18" s="65" t="s">
+      <c r="F18" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="G18" s="58" t="s">
+      <c r="G18" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="H18" s="66"/>
-      <c r="I18" s="61">
+      <c r="H18" s="63"/>
+      <c r="I18" s="58">
         <v>0.1</v>
       </c>
-      <c r="J18" s="60">
+      <c r="J18" s="57">
         <v>60</v>
       </c>
-      <c r="K18" s="66"/>
-      <c r="L18" s="61">
+      <c r="K18" s="63"/>
+      <c r="L18" s="58">
         <v>0.1</v>
       </c>
-      <c r="M18" s="66" t="s">
+      <c r="M18" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="P18" s="67"/>
-      <c r="Q18" s="68"/>
-      <c r="R18" s="68"/>
-      <c r="S18" s="69"/>
-      <c r="U18" s="67"/>
-      <c r="V18" s="68"/>
-      <c r="W18" s="68"/>
-      <c r="X18" s="70"/>
-      <c r="AA18" s="32" t="s">
+      <c r="P18" s="64"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="66"/>
+      <c r="U18" s="64"/>
+      <c r="V18" s="65"/>
+      <c r="W18" s="65"/>
+      <c r="X18" s="67"/>
+      <c r="AA18" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="AB18" s="32" t="s">
+      <c r="AB18" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="AC18" s="32" t="s">
+      <c r="AC18" s="29" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A19" s="41"/>
-      <c r="B19" s="18" t="s">
+      <c r="A19" s="38"/>
+      <c r="B19" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="57">
+      <c r="E19" s="54">
         <v>0.1</v>
       </c>
-      <c r="F19" s="59"/>
-      <c r="G19" s="58" t="s">
+      <c r="F19" s="56"/>
+      <c r="G19" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="H19" s="60"/>
-      <c r="I19" s="61">
+      <c r="H19" s="57"/>
+      <c r="I19" s="58">
         <v>0.1</v>
       </c>
-      <c r="J19" s="60">
+      <c r="J19" s="57">
         <v>60</v>
       </c>
-      <c r="K19" s="60"/>
-      <c r="L19" s="61">
+      <c r="K19" s="57"/>
+      <c r="L19" s="58">
         <v>0.1</v>
       </c>
-      <c r="M19" s="60" t="s">
+      <c r="M19" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="X19" s="15"/>
-      <c r="AA19" s="32" t="s">
+      <c r="X19" s="14"/>
+      <c r="AA19" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="AB19" s="32" t="s">
+      <c r="AB19" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="AC19" s="32" t="s">
+      <c r="AC19" s="29" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="18" t="s">
+      <c r="A20" s="16"/>
+      <c r="B20" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="62">
+      <c r="E20" s="59">
         <v>0.12</v>
       </c>
-      <c r="F20" s="71"/>
-      <c r="G20" s="58" t="s">
+      <c r="F20" s="68"/>
+      <c r="G20" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="H20" s="66"/>
-      <c r="I20" s="61">
+      <c r="H20" s="63"/>
+      <c r="I20" s="58">
         <v>0.1</v>
       </c>
-      <c r="J20" s="60">
+      <c r="J20" s="57">
         <v>60</v>
       </c>
-      <c r="K20" s="66"/>
-      <c r="L20" s="61">
+      <c r="K20" s="63"/>
+      <c r="L20" s="58">
         <v>0.1</v>
       </c>
-      <c r="M20" s="66" t="s">
+      <c r="M20" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="R20" s="72" t="s">
+      <c r="R20" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="AA20" s="32" t="s">
+      <c r="AA20" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="AB20" s="32" t="s">
+      <c r="AB20" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="AC20" s="32" t="s">
+      <c r="AC20" s="29" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="57">
+      <c r="E21" s="54">
         <v>0.1</v>
       </c>
-      <c r="F21" s="65" t="s">
+      <c r="F21" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="G21" s="58" t="s">
+      <c r="G21" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="H21" s="66"/>
-      <c r="I21" s="61">
+      <c r="H21" s="63"/>
+      <c r="I21" s="58">
         <v>0.1</v>
       </c>
-      <c r="J21" s="60">
+      <c r="J21" s="57">
         <v>60</v>
       </c>
-      <c r="K21" s="66"/>
-      <c r="L21" s="61">
+      <c r="K21" s="63"/>
+      <c r="L21" s="58">
         <v>0.1</v>
       </c>
-      <c r="M21" s="60" t="s">
+      <c r="M21" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="R21" s="73" t="s">
+      <c r="R21" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="AA21" s="32" t="s">
+      <c r="AA21" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AB21" s="32" t="s">
+      <c r="AB21" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="AC21" s="32" t="s">
+      <c r="AC21" s="29" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N22" s="74"/>
-      <c r="AA22" s="32" t="s">
+      <c r="N22" s="71"/>
+      <c r="AA22" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="AB22" s="32" t="s">
+      <c r="AB22" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="AC22" s="32" t="s">
+      <c r="AC22" s="29" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="143" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
-      <c r="J23" s="75"/>
-      <c r="K23" s="75"/>
-      <c r="L23" s="75"/>
-      <c r="M23" s="75"/>
-      <c r="N23" s="74"/>
-      <c r="R23" s="72" t="s">
+      <c r="C23" s="143"/>
+      <c r="D23" s="143"/>
+      <c r="E23" s="143"/>
+      <c r="F23" s="143"/>
+      <c r="G23" s="143"/>
+      <c r="H23" s="143"/>
+      <c r="I23" s="143"/>
+      <c r="J23" s="143"/>
+      <c r="K23" s="143"/>
+      <c r="L23" s="143"/>
+      <c r="M23" s="143"/>
+      <c r="N23" s="71"/>
+      <c r="R23" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="V23" s="76" t="s">
+      <c r="V23" s="72" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B24" s="77" t="s">
+      <c r="B24" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="77"/>
-      <c r="K24" s="77"/>
-      <c r="L24" s="77"/>
-      <c r="M24" s="77"/>
-      <c r="R24" s="73" t="s">
+      <c r="C24" s="139"/>
+      <c r="D24" s="139"/>
+      <c r="E24" s="139"/>
+      <c r="F24" s="139"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="139"/>
+      <c r="I24" s="139"/>
+      <c r="J24" s="139"/>
+      <c r="K24" s="139"/>
+      <c r="L24" s="139"/>
+      <c r="M24" s="139"/>
+      <c r="R24" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="V24" s="73" t="s">
+      <c r="V24" s="70" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B25" s="77" t="s">
+      <c r="B25" s="139" t="s">
         <v>111</v>
       </c>
-      <c r="C25" s="77"/>
-      <c r="D25" s="77"/>
-      <c r="E25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="77"/>
-      <c r="K25" s="77"/>
-      <c r="L25" s="77"/>
-      <c r="M25" s="77"/>
-      <c r="V25" s="78"/>
-      <c r="W25" s="78"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="139"/>
+      <c r="I25" s="139"/>
+      <c r="J25" s="139"/>
+      <c r="K25" s="139"/>
+      <c r="L25" s="139"/>
+      <c r="M25" s="139"/>
+      <c r="V25" s="144"/>
+      <c r="W25" s="144"/>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B26" s="77" t="s">
+      <c r="B26" s="139" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="77"/>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="77"/>
-      <c r="K26" s="77"/>
-      <c r="L26" s="77"/>
-      <c r="M26" s="77"/>
-      <c r="N26" s="79"/>
-      <c r="R26" s="72" t="s">
+      <c r="C26" s="139"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="139"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="139"/>
+      <c r="L26" s="139"/>
+      <c r="M26" s="139"/>
+      <c r="N26" s="73"/>
+      <c r="R26" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="V26" s="72" t="s">
+      <c r="V26" s="69" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
-      <c r="K27" s="77"/>
-      <c r="L27" s="77"/>
-      <c r="M27" s="77"/>
-      <c r="N27" s="79"/>
+      <c r="C27" s="139"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="139"/>
+      <c r="H27" s="139"/>
+      <c r="I27" s="139"/>
+      <c r="J27" s="139"/>
+      <c r="K27" s="139"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="139"/>
+      <c r="N27" s="73"/>
       <c r="R27" s="1" t="s">
         <v>116</v>
       </c>
@@ -68109,21 +68086,21 @@
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B28" s="77" t="s">
+      <c r="B28" s="139" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="77"/>
-      <c r="K28" s="77"/>
-      <c r="L28" s="77"/>
-      <c r="M28" s="77"/>
-      <c r="N28" s="79"/>
+      <c r="C28" s="139"/>
+      <c r="D28" s="139"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="139"/>
+      <c r="G28" s="139"/>
+      <c r="H28" s="139"/>
+      <c r="I28" s="139"/>
+      <c r="J28" s="139"/>
+      <c r="K28" s="139"/>
+      <c r="L28" s="139"/>
+      <c r="M28" s="139"/>
+      <c r="N28" s="73"/>
       <c r="R28" s="1" t="s">
         <v>119</v>
       </c>
@@ -68132,20 +68109,20 @@
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B29" s="77" t="s">
+      <c r="B29" s="139" t="s">
         <v>121</v>
       </c>
-      <c r="C29" s="77"/>
-      <c r="D29" s="77"/>
-      <c r="E29" s="77"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="77"/>
-      <c r="K29" s="77"/>
-      <c r="L29" s="77"/>
-      <c r="M29" s="77"/>
+      <c r="C29" s="139"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="139"/>
+      <c r="H29" s="139"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="139"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="139"/>
+      <c r="M29" s="139"/>
       <c r="R29" s="1" t="s">
         <v>122</v>
       </c>
@@ -68154,20 +68131,20 @@
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B30" s="80" t="s">
+      <c r="B30" s="138" t="s">
         <v>124</v>
       </c>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="80"/>
-      <c r="J30" s="80"/>
-      <c r="K30" s="80"/>
-      <c r="L30" s="80"/>
-      <c r="M30" s="80"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="138"/>
+      <c r="E30" s="138"/>
+      <c r="F30" s="138"/>
+      <c r="G30" s="138"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="138"/>
+      <c r="J30" s="138"/>
+      <c r="K30" s="138"/>
+      <c r="L30" s="138"/>
+      <c r="M30" s="138"/>
       <c r="R30" s="1" t="s">
         <v>125</v>
       </c>
@@ -68176,21 +68153,21 @@
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B31" s="80" t="s">
+      <c r="B31" s="138" t="s">
         <v>127</v>
       </c>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="80"/>
-      <c r="M31" s="80"/>
-      <c r="R31" s="73" t="s">
+      <c r="C31" s="138"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="138"/>
+      <c r="K31" s="138"/>
+      <c r="L31" s="138"/>
+      <c r="M31" s="138"/>
+      <c r="R31" s="70" t="s">
         <v>128</v>
       </c>
       <c r="W31" s="1" t="s">
@@ -68198,120 +68175,120 @@
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B32" s="80" t="s">
+      <c r="B32" s="138" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="80"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="80"/>
-      <c r="G32" s="80"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80"/>
-      <c r="M32" s="80"/>
+      <c r="C32" s="138"/>
+      <c r="D32" s="138"/>
+      <c r="E32" s="138"/>
+      <c r="F32" s="138"/>
+      <c r="G32" s="138"/>
+      <c r="H32" s="138"/>
+      <c r="I32" s="138"/>
+      <c r="J32" s="138"/>
+      <c r="K32" s="138"/>
+      <c r="L32" s="138"/>
+      <c r="M32" s="138"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B33" s="77" t="s">
+      <c r="B33" s="139" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="77"/>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="77"/>
-      <c r="J33" s="77"/>
-      <c r="K33" s="77"/>
-      <c r="L33" s="77"/>
-      <c r="M33" s="77"/>
+      <c r="C33" s="139"/>
+      <c r="D33" s="139"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="139"/>
+      <c r="G33" s="139"/>
+      <c r="H33" s="139"/>
+      <c r="I33" s="139"/>
+      <c r="J33" s="139"/>
+      <c r="K33" s="139"/>
+      <c r="L33" s="139"/>
+      <c r="M33" s="139"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B34" s="81"/>
-      <c r="C34" s="81"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="81"/>
-      <c r="K34" s="81"/>
-      <c r="L34" s="81"/>
-      <c r="M34" s="81"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="74"/>
+      <c r="I34" s="74"/>
+      <c r="J34" s="74"/>
+      <c r="K34" s="74"/>
+      <c r="L34" s="74"/>
+      <c r="M34" s="74"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B35" s="82" t="s">
+      <c r="B35" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="74"/>
-      <c r="I35" s="74"/>
-      <c r="J35" s="74"/>
-      <c r="K35" s="74"/>
-      <c r="L35" s="74"/>
-      <c r="M35" s="74"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="71"/>
+      <c r="L35" s="71"/>
+      <c r="M35" s="71"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C36" s="74"/>
-      <c r="D36" s="74"/>
-      <c r="E36" s="74"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="74"/>
-      <c r="I36" s="74"/>
-      <c r="J36" s="74"/>
-      <c r="K36" s="74"/>
-      <c r="L36" s="74"/>
-      <c r="M36" s="74"/>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="71"/>
+      <c r="L36" s="71"/>
+      <c r="M36" s="71"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C37" s="74"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="74"/>
-      <c r="H37" s="74"/>
-      <c r="I37" s="74"/>
-      <c r="J37" s="74"/>
-      <c r="K37" s="74"/>
-      <c r="L37" s="74"/>
-      <c r="M37" s="74"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+      <c r="K37" s="71"/>
+      <c r="L37" s="71"/>
+      <c r="M37" s="71"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B38" s="74"/>
-      <c r="C38" s="74"/>
-      <c r="D38" s="74"/>
-      <c r="E38" s="74"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="74"/>
-      <c r="H38" s="74"/>
-      <c r="I38" s="74"/>
-      <c r="J38" s="74"/>
-      <c r="K38" s="74"/>
-      <c r="L38" s="74"/>
-      <c r="M38" s="74"/>
+      <c r="B38" s="71"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="71"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B39" s="83"/>
+      <c r="B39" s="76"/>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B42" s="72"/>
+      <c r="B42" s="69"/>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B43" s="84"/>
-      <c r="C43" s="84"/>
-      <c r="D43" s="84"/>
+      <c r="B43" s="140"/>
+      <c r="C43" s="140"/>
+      <c r="D43" s="140"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:M21" xr:uid="{27C47C64-5BA2-4774-BE4B-59B66BC9B742}">
@@ -68338,6 +68315,13 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="16">
+    <mergeCell ref="B25:M25"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="Q1:W2"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="V4:X4"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="B24:M24"/>
     <mergeCell ref="B32:M32"/>
     <mergeCell ref="B33:M33"/>
     <mergeCell ref="B43:D43"/>
@@ -68347,13 +68331,6 @@
     <mergeCell ref="B29:M29"/>
     <mergeCell ref="B30:M30"/>
     <mergeCell ref="B31:M31"/>
-    <mergeCell ref="Q1:W2"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="B24:M24"/>
-    <mergeCell ref="B25:M25"/>
-    <mergeCell ref="V25:W25"/>
   </mergeCells>
   <conditionalFormatting sqref="T4 X4 T6:T17 X6:X19">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="VB">
@@ -68382,7 +68359,7 @@
   <cols>
     <col min="1" max="1" width="2.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" style="1"/>
-    <col min="3" max="3" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" style="1" bestFit="1" customWidth="1"/>
@@ -68393,537 +68370,537 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="85" t="s">
+      <c r="C2" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="78" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="137" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
     </row>
     <row r="5" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
     </row>
     <row r="6" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="11"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="14"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="26"/>
-      <c r="C7" s="88" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="89" t="str">
+      <c r="D7" s="81" t="str">
         <f>VLOOKUP(C7,'Condiciones Comerciales'!$B$3:$C$21,2,FALSE)</f>
         <v>Pre-entrega</v>
       </c>
-      <c r="H7" s="34"/>
+      <c r="H7" s="31"/>
     </row>
     <row r="8" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="26"/>
-      <c r="H8" s="34"/>
+      <c r="B8" s="25"/>
+      <c r="H8" s="31"/>
     </row>
     <row r="9" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="26"/>
-      <c r="D9" s="72" t="s">
+      <c r="B9" s="25"/>
+      <c r="D9" s="69" t="s">
         <v>137</v>
       </c>
       <c r="F9"/>
-      <c r="H9" s="34"/>
+      <c r="H9" s="31"/>
     </row>
     <row r="10" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="26"/>
-      <c r="C10" s="90" t="s">
+      <c r="B10" s="25"/>
+      <c r="C10" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="D10" s="91">
+      <c r="D10" s="83">
         <v>3319</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="31"/>
     </row>
     <row r="11" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="26"/>
-      <c r="C11" s="90" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="82" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="91">
+      <c r="D11" s="83">
         <v>350</v>
       </c>
-      <c r="F11" s="72"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="93"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="85"/>
     </row>
     <row r="12" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="26"/>
-      <c r="C12" s="90" t="s">
+      <c r="B12" s="25"/>
+      <c r="C12" s="82" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="91">
+      <c r="D12" s="83">
         <v>80</v>
       </c>
-      <c r="F12" s="94"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="96"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="88"/>
     </row>
     <row r="13" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="26"/>
-      <c r="D13" s="97">
+      <c r="B13" s="25"/>
+      <c r="D13" s="89">
         <f>SUM(D10:D12)</f>
         <v>3749</v>
       </c>
-      <c r="F13" s="94"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="96"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="88"/>
     </row>
     <row r="14" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="26"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="96"/>
+      <c r="B14" s="25"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="88"/>
     </row>
     <row r="15" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="26"/>
-      <c r="C15" s="98" t="s">
+      <c r="B15" s="25"/>
+      <c r="C15" s="145" t="s">
         <v>141</v>
       </c>
-      <c r="D15" s="99">
+      <c r="D15" s="91">
         <f>VLOOKUP(C7,'Condiciones Comerciales'!B3:E21,4,FALSE)</f>
         <v>0.13</v>
       </c>
-      <c r="F15" s="94"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="96"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="87"/>
+      <c r="H15" s="88"/>
     </row>
     <row r="16" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="26"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="100"/>
-      <c r="H16" s="96"/>
+      <c r="B16" s="25"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="88"/>
     </row>
     <row r="17" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="26"/>
-      <c r="D17" s="72" t="s">
+      <c r="B17" s="25"/>
+      <c r="D17" s="69" t="s">
         <v>142</v>
       </c>
-      <c r="G17" s="101"/>
-      <c r="H17" s="34"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="31"/>
     </row>
     <row r="18" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="26"/>
-      <c r="C18" s="1" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="146" t="s">
         <v>143</v>
       </c>
-      <c r="D18" s="95">
+      <c r="D18" s="147">
         <f>D10*(100%-D15)</f>
         <v>2887.53</v>
       </c>
-      <c r="H18" s="34"/>
+      <c r="H18" s="31"/>
     </row>
     <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="26"/>
-      <c r="C19" s="1" t="s">
+      <c r="B19" s="25"/>
+      <c r="C19" s="146" t="s">
         <v>144</v>
       </c>
-      <c r="D19" s="95">
+      <c r="D19" s="147">
         <f>D11</f>
         <v>350</v>
       </c>
-      <c r="F19" s="72"/>
-      <c r="G19" s="92"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="93"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="85"/>
     </row>
     <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="26"/>
-      <c r="C20" s="1" t="s">
+      <c r="B20" s="25"/>
+      <c r="C20" s="146" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="95">
+      <c r="D20" s="147">
         <f>D12</f>
         <v>80</v>
       </c>
-      <c r="F20" s="94"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="102"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="92"/>
+      <c r="H20" s="94"/>
     </row>
     <row r="21" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="26"/>
-      <c r="C21" s="72" t="s">
+      <c r="B21" s="25"/>
+      <c r="C21" s="148" t="s">
         <v>145</v>
       </c>
-      <c r="D21" s="103">
+      <c r="D21" s="149">
         <f>SUM(D18:D20)</f>
         <v>3317.53</v>
       </c>
-      <c r="F21" s="94"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="102"/>
+      <c r="F21" s="86"/>
+      <c r="G21" s="92"/>
+      <c r="H21" s="94"/>
     </row>
     <row r="22" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="26"/>
-      <c r="F22" s="104" t="s">
+      <c r="B22" s="25"/>
+      <c r="F22" s="95" t="s">
         <v>146</v>
       </c>
-      <c r="G22" s="100"/>
-      <c r="H22" s="102"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="94"/>
     </row>
     <row r="23" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="26"/>
-      <c r="C23" s="98" t="s">
+      <c r="B23" s="25"/>
+      <c r="C23" s="150" t="s">
         <v>147</v>
       </c>
-      <c r="D23" s="105">
+      <c r="D23" s="151">
         <v>0.1</v>
       </c>
-      <c r="F23" s="94"/>
-      <c r="G23" s="106" t="s">
+      <c r="F23" s="86"/>
+      <c r="G23" s="96" t="s">
         <v>148</v>
       </c>
-      <c r="H23" s="107">
+      <c r="H23" s="97">
         <v>39801.980000000003</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="26"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="102"/>
+      <c r="B24" s="25"/>
+      <c r="F24" s="86"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="94"/>
     </row>
     <row r="25" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="26"/>
-      <c r="C25" s="108" t="s">
+      <c r="B25" s="25"/>
+      <c r="C25" s="152" t="s">
         <v>149</v>
       </c>
-      <c r="D25" s="109">
+      <c r="D25" s="153">
         <f>100000/H23</f>
         <v>2.512437823444964</v>
       </c>
-      <c r="E25" s="110">
+      <c r="E25" s="98">
         <f>D25/$D$21</f>
         <v>7.573218097334354E-4</v>
       </c>
-      <c r="F25" s="111"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="112"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="99"/>
+      <c r="H25" s="100"/>
     </row>
     <row r="26" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="26"/>
-      <c r="C26" s="113" t="s">
+      <c r="B26" s="25"/>
+      <c r="C26" s="154" t="s">
         <v>150</v>
       </c>
-      <c r="D26" s="105">
+      <c r="D26" s="151">
         <v>0.02</v>
       </c>
-      <c r="E26" s="110"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="112"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="100"/>
     </row>
     <row r="27" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="26"/>
-      <c r="C27" s="108" t="s">
+      <c r="B27" s="25"/>
+      <c r="C27" s="152" t="s">
         <v>151</v>
       </c>
-      <c r="D27" s="114">
+      <c r="D27" s="155">
         <f>D21*D26</f>
         <v>66.3506</v>
       </c>
-      <c r="E27" s="110">
+      <c r="E27" s="98">
         <f>D27/$D$21</f>
         <v>0.02</v>
       </c>
-      <c r="F27" s="111"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="112"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="99"/>
+      <c r="H27" s="100"/>
     </row>
     <row r="28" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="26"/>
-      <c r="C28" s="115" t="s">
+      <c r="B28" s="25"/>
+      <c r="C28" s="156" t="s">
         <v>152</v>
       </c>
-      <c r="D28" s="116">
+      <c r="D28" s="155">
         <f>IF(D23=0%,0,D21*D23-D25-D27)</f>
         <v>262.88996217655512</v>
       </c>
-      <c r="E28" s="110">
+      <c r="E28" s="98">
         <f>D28/$D$21</f>
         <v>7.9242678190266577E-2</v>
       </c>
-      <c r="F28" s="117" t="str">
+      <c r="F28" s="102" t="str">
         <f>IF(D7="Inmediata","* Mutuo Maestra 60 cuotas de:", "* Cuotas sin interés desde:")</f>
         <v>* Cuotas sin interés desde:</v>
       </c>
-      <c r="G28" s="118">
+      <c r="G28" s="103">
         <f>IF(D7="Inmediata",-PMT(5%/12,60,D28),7)</f>
         <v>7</v>
       </c>
-      <c r="H28" s="119">
+      <c r="H28" s="104">
         <f>+G28*H23</f>
         <v>278613.86000000004</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="26"/>
+      <c r="B29" s="25"/>
       <c r="C29" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D29" s="116">
+      <c r="D29" s="101">
         <f>+D21*(100%-D23)</f>
         <v>2985.777</v>
       </c>
-      <c r="E29" s="110">
+      <c r="E29" s="98">
         <f>D29/$D$21</f>
         <v>0.89999999999999991</v>
       </c>
-      <c r="F29" s="117" t="str">
+      <c r="F29" s="102" t="str">
         <f>IF(G28=7,"Cuotas de UF 7:","")</f>
         <v>Cuotas de UF 7:</v>
       </c>
-      <c r="G29" s="120">
+      <c r="G29" s="105">
         <f>IF(G28=7,ROUNDDOWN(D28/7,0),"")</f>
         <v>37</v>
       </c>
-      <c r="H29" s="121"/>
+      <c r="H29" s="106"/>
     </row>
     <row r="30" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="26"/>
-      <c r="D30" s="116"/>
-      <c r="E30" s="122"/>
-      <c r="F30" s="117" t="str">
+      <c r="B30" s="25"/>
+      <c r="D30" s="101"/>
+      <c r="E30" s="107"/>
+      <c r="F30" s="102" t="str">
         <f>IF(G28=7,"Diferencia cuota adicional:","")</f>
         <v>Diferencia cuota adicional:</v>
       </c>
-      <c r="G30" s="118">
+      <c r="G30" s="103">
         <f>IF(G28=7,D28-(G28*G29),"")</f>
         <v>3.889962176555116</v>
       </c>
-      <c r="H30" s="112"/>
+      <c r="H30" s="100"/>
     </row>
     <row r="31" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="26"/>
-      <c r="C31" s="149" t="s">
-        <v>173</v>
-      </c>
-      <c r="D31" s="150">
+      <c r="B31" s="25"/>
+      <c r="C31" s="132" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" s="133">
         <v>0.1</v>
       </c>
-      <c r="F31" s="123" t="str">
+      <c r="F31" s="108" t="str">
         <f>IF(G28=7,"Máximo de cuotas Proyecto:","")</f>
         <v>Máximo de cuotas Proyecto:</v>
       </c>
-      <c r="G31" s="124">
+      <c r="G31" s="109">
         <f>IF(G28=7,VLOOKUP(C7,'Condiciones Comerciales'!B3:J21,9,FALSE),"")</f>
         <v>60</v>
       </c>
-      <c r="H31" s="125" t="str">
+      <c r="H31" s="110" t="str">
         <f>IF(G28=7,IF(G31&gt;=(G29+1),"OK","No Cumple"),"")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="26"/>
-      <c r="C32" s="126"/>
-      <c r="D32" s="127"/>
-      <c r="F32" s="117" t="str">
+      <c r="B32" s="25"/>
+      <c r="C32" s="111"/>
+      <c r="D32" s="112"/>
+      <c r="F32" s="102" t="str">
         <f>IF(H31="No Cumple","Debe pagar cuotas de:","")</f>
         <v/>
       </c>
-      <c r="G32" s="118" t="str">
+      <c r="G32" s="103" t="str">
         <f>IF(H31="No Cumple",D28/G31,"")</f>
         <v/>
       </c>
-      <c r="H32" s="119" t="str">
+      <c r="H32" s="104" t="str">
         <f>IF(F32&lt;&gt;"",G32*H23,"")</f>
         <v/>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="26"/>
-      <c r="C33" s="98" t="s">
+      <c r="B33" s="25"/>
+      <c r="C33" s="90" t="s">
         <v>154</v>
       </c>
-      <c r="D33" s="128">
+      <c r="D33" s="113">
         <f>100%-D23-D31</f>
         <v>0.8</v>
       </c>
-      <c r="H33" s="34"/>
-    </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="26"/>
-      <c r="C34" s="126"/>
-      <c r="D34" s="127"/>
-      <c r="H34" s="34"/>
-    </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="26"/>
-      <c r="C35" s="129" t="s">
+      <c r="H33" s="31"/>
+    </row>
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="25"/>
+      <c r="C34" s="111"/>
+      <c r="D34" s="112"/>
+      <c r="H34" s="31"/>
+    </row>
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="25"/>
+      <c r="C35" s="160" t="s">
         <v>155</v>
       </c>
-      <c r="D35" s="130">
+      <c r="D35" s="161">
         <f>D29/D33</f>
         <v>3732.2212500000001</v>
       </c>
-      <c r="H35" s="34"/>
+      <c r="H35" s="31"/>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="26"/>
-      <c r="C36" s="151" t="s">
-        <v>174</v>
-      </c>
-      <c r="D36" s="152">
+      <c r="B36" s="25"/>
+      <c r="C36" s="134" t="s">
+        <v>173</v>
+      </c>
+      <c r="D36" s="135">
         <f>D35-D37-D38</f>
         <v>414.69124999999985</v>
       </c>
-      <c r="E36" s="153">
+      <c r="E36" s="136">
         <f>D36/$D$35</f>
         <v>0.11111111111111108</v>
       </c>
-      <c r="H36" s="34"/>
+      <c r="H36" s="31"/>
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="26"/>
-      <c r="C37" s="126" t="s">
+      <c r="B37" s="25"/>
+      <c r="C37" s="157" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="103">
+      <c r="D37" s="158">
         <f>D25+D27+D28</f>
         <v>331.7530000000001</v>
       </c>
-      <c r="E37" s="110">
+      <c r="E37" s="159">
         <f t="shared" ref="E37:E38" si="0">D37/$D$35</f>
         <v>8.888888888888892E-2</v>
       </c>
-      <c r="H37" s="34"/>
+      <c r="H37" s="31"/>
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="26"/>
-      <c r="C38" s="126" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="103">
+      <c r="B38" s="25"/>
+      <c r="C38" s="157" t="s">
+        <v>174</v>
+      </c>
+      <c r="D38" s="158">
         <f>D35*D33</f>
         <v>2985.777</v>
       </c>
-      <c r="E38" s="110">
+      <c r="E38" s="159">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="F38" s="131" t="s">
-        <v>158</v>
-      </c>
-      <c r="G38" s="132">
+      <c r="F38" s="114" t="s">
+        <v>157</v>
+      </c>
+      <c r="G38" s="115">
         <f>PMT(4%/12,300,-D38)</f>
         <v>15.760030975137768</v>
       </c>
-      <c r="H38" s="133">
+      <c r="H38" s="116">
         <f>+G38*H23</f>
         <v>627280.437671814</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="67"/>
-      <c r="C39" s="134"/>
-      <c r="D39" s="135"/>
-      <c r="E39" s="136"/>
-      <c r="F39" s="137"/>
-      <c r="G39" s="138"/>
-      <c r="H39" s="69"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="117"/>
+      <c r="D39" s="118"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="120"/>
+      <c r="G39" s="121"/>
+      <c r="H39" s="66"/>
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="26"/>
-      <c r="C40" s="126"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="110"/>
-      <c r="F40" s="131"/>
-      <c r="G40" s="132"/>
-      <c r="H40" s="34"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="111"/>
+      <c r="D40" s="84"/>
+      <c r="E40" s="98"/>
+      <c r="F40" s="114"/>
+      <c r="G40" s="115"/>
+      <c r="H40" s="31"/>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="26"/>
-      <c r="C41" s="98" t="s">
+      <c r="B41" s="25"/>
+      <c r="C41" s="90" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="113"/>
+      <c r="E41" s="98"/>
+      <c r="F41" s="114"/>
+      <c r="G41" s="115"/>
+      <c r="H41" s="31"/>
+    </row>
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="25"/>
+      <c r="C42" s="111"/>
+      <c r="D42" s="84"/>
+      <c r="E42" s="98"/>
+      <c r="F42" s="114"/>
+      <c r="G42" s="115"/>
+      <c r="H42" s="31"/>
+    </row>
+    <row r="43" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="25"/>
+      <c r="C43" s="122" t="s">
         <v>159</v>
       </c>
-      <c r="D41" s="128"/>
-      <c r="E41" s="110"/>
-      <c r="F41" s="131"/>
-      <c r="G41" s="132"/>
-      <c r="H41" s="34"/>
-    </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="26"/>
-      <c r="C42" s="126"/>
-      <c r="D42" s="92"/>
-      <c r="E42" s="110"/>
-      <c r="F42" s="131"/>
-      <c r="G42" s="132"/>
-      <c r="H42" s="34"/>
-    </row>
-    <row r="43" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="26"/>
-      <c r="C43" s="139" t="s">
-        <v>160</v>
-      </c>
-      <c r="D43" s="140">
+      <c r="D43" s="123">
         <f>800000/H23</f>
         <v>20.099502587559712</v>
       </c>
-      <c r="E43" s="141"/>
-      <c r="F43" s="142" t="s">
+      <c r="E43" s="124"/>
+      <c r="F43" s="125" t="s">
+        <v>160</v>
+      </c>
+      <c r="G43" s="115"/>
+      <c r="H43" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="G43" s="132"/>
-      <c r="H43" s="35" t="s">
+    </row>
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="25"/>
+      <c r="C44" s="122" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="26"/>
-      <c r="C44" s="139" t="s">
-        <v>163</v>
-      </c>
-      <c r="D44" s="140">
+      <c r="D44" s="123">
         <f>380000/H23</f>
         <v>9.5472637290908633</v>
       </c>
-      <c r="E44" s="141"/>
-      <c r="F44" s="142" t="s">
-        <v>164</v>
-      </c>
-      <c r="G44" s="132"/>
-      <c r="H44" s="143">
+      <c r="E44" s="124"/>
+      <c r="F44" s="125" t="s">
+        <v>163</v>
+      </c>
+      <c r="G44" s="115"/>
+      <c r="H44" s="126">
         <f>+D43/24+D44-G38</f>
         <v>-5.3752879715652497</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="67"/>
-      <c r="C45" s="68"/>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="68"/>
-      <c r="H45" s="144">
+      <c r="B45" s="64"/>
+      <c r="C45" s="65"/>
+      <c r="D45" s="65"/>
+      <c r="E45" s="65"/>
+      <c r="F45" s="65"/>
+      <c r="G45" s="65"/>
+      <c r="H45" s="127">
         <f>+H44*H23</f>
         <v>-213947.10433848065</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D46" s="100"/>
+      <c r="D46" s="92"/>
     </row>
     <row r="49" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C49" t="s">
@@ -68935,2929 +68912,2929 @@
     </row>
     <row r="50" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
+        <v>164</v>
+      </c>
+      <c r="D50" t="s">
         <v>165</v>
-      </c>
-      <c r="D50" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="52" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" s="128" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="129">
+        <v>13</v>
+      </c>
+      <c r="D53" s="128">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="130" t="s">
         <v>167</v>
       </c>
-      <c r="D52" s="145" t="s">
+      <c r="D54" s="128">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D55" s="128">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C56" s="129">
+        <v>32</v>
+      </c>
+      <c r="D56" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D57" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C58" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D58" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C59" s="129">
+        <v>34</v>
+      </c>
+      <c r="D59" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C60" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D60" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C61" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D61" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="62" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C62" s="129">
+        <v>35</v>
+      </c>
+      <c r="D62" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C63" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D63" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="64" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C64" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D64" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="129">
+        <v>7</v>
+      </c>
+      <c r="D65" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C66" s="130" t="s">
+        <v>167</v>
+      </c>
+      <c r="D66" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C67" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D67" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C68" s="129">
+        <v>36</v>
+      </c>
+      <c r="D68" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C69" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D69" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C70" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D70" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="71" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C71" s="129">
+        <v>10</v>
+      </c>
+      <c r="D71" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="130" t="s">
+        <v>167</v>
+      </c>
+      <c r="D72" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="73" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C73" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D73" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="74" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C74" s="129">
+        <v>37</v>
+      </c>
+      <c r="D74" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C75" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D75" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="76" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D76" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="129">
+        <v>5</v>
+      </c>
+      <c r="D77" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="78" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C78" s="130" t="s">
+        <v>167</v>
+      </c>
+      <c r="D78" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="79" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C79" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D79" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="80" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C80" s="129">
+        <v>38</v>
+      </c>
+      <c r="D80" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="81" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C81" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D81" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="82" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C82" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D82" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="83" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C83" s="129">
+        <v>20</v>
+      </c>
+      <c r="D83" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="84" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C84" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D84" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="85" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C85" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D85" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="86" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C86" s="129">
+        <v>39</v>
+      </c>
+      <c r="D86" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="87" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C87" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D87" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="88" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C88" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D88" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="89" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C89" s="129">
+        <v>24</v>
+      </c>
+      <c r="D89" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="90" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C90" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D90" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="91" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C91" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D91" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="92" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C92" s="129">
+        <v>40</v>
+      </c>
+      <c r="D92" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="93" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C93" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D93" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="94" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C94" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D94" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="95" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C95" s="129">
+        <v>26</v>
+      </c>
+      <c r="D95" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="96" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C96" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D96" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="97" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C97" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D97" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="98" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="129">
+        <v>41</v>
+      </c>
+      <c r="D98" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="99" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C99" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D99" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="100" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C100" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D100" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="101" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C101" s="129">
+        <v>28</v>
+      </c>
+      <c r="D101" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="102" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C102" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D102" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="103" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C103" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D103" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="104" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C104" s="129">
+        <v>43</v>
+      </c>
+      <c r="D104" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="105" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C105" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D105" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="106" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C106" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D106" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="107" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C107" s="129">
+        <v>31</v>
+      </c>
+      <c r="D107" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="108" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C108" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D108" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="109" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C109" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D109" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="110" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C110" s="129">
+        <v>44</v>
+      </c>
+      <c r="D110" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="111" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C111" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D111" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="112" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C112" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D112" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="113" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C113" s="129">
+        <v>6</v>
+      </c>
+      <c r="D113" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="114" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C114" s="130" t="s">
+        <v>167</v>
+      </c>
+      <c r="D114" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="115" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C115" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D115" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="116" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C116" s="129">
+        <v>45</v>
+      </c>
+      <c r="D116" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="117" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C117" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D117" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="118" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C118" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D118" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="119" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C119" s="129">
+        <v>11</v>
+      </c>
+      <c r="D119" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="120" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C120" s="130" t="s">
+        <v>167</v>
+      </c>
+      <c r="D120" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="121" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C121" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D121" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="122" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C122" s="129">
+        <v>46</v>
+      </c>
+      <c r="D122" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="123" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C123" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D123" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="124" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C124" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D124" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="125" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C125" s="129">
+        <v>23</v>
+      </c>
+      <c r="D125" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="126" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C126" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D126" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="127" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C127" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D127" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="128" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C128" s="129">
+        <v>47</v>
+      </c>
+      <c r="D128" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="129" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C129" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D129" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="130" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C130" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D130" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="131" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C131" s="129">
+        <v>27</v>
+      </c>
+      <c r="D131" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="132" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C132" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D132" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="133" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C133" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D133" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="134" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C134" s="129">
+        <v>48</v>
+      </c>
+      <c r="D134" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="135" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C135" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D135" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="136" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C136" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D136" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="137" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C137" s="129">
+        <v>4</v>
+      </c>
+      <c r="D137" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="138" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C138" s="130" t="s">
+        <v>167</v>
+      </c>
+      <c r="D138" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="139" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C139" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D139" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="140" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C140" s="129">
+        <v>49</v>
+      </c>
+      <c r="D140" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="141" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C141" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D141" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="142" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C142" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D142" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="143" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C143" s="129">
+        <v>19</v>
+      </c>
+      <c r="D143" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="144" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C144" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D144" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="145" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C145" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D145" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="146" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C146" s="129">
+        <v>50</v>
+      </c>
+      <c r="D146" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="147" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C147" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D147" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="148" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C148" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D148" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="149" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C149" s="129">
+        <v>29</v>
+      </c>
+      <c r="D149" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="150" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C150" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D150" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="151" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C151" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D151" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="152" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" s="129">
+        <v>51</v>
+      </c>
+      <c r="D152" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="153" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D153" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="154" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C154" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D154" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="155" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C155" s="129">
+        <v>25</v>
+      </c>
+      <c r="D155" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="156" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C156" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D156" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="157" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C157" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D157" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="158" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C158" s="129">
+        <v>52</v>
+      </c>
+      <c r="D158" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="159" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C159" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D159" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="160" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C160" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D160" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="161" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C161" s="129">
+        <v>9</v>
+      </c>
+      <c r="D161" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="162" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C162" s="130" t="s">
+        <v>167</v>
+      </c>
+      <c r="D162" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="163" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C163" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D163" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="164" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C164" s="129">
+        <v>54</v>
+      </c>
+      <c r="D164" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="165" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C165" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D165" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="166" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C166" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D166" s="128">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="167" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C167" s="129">
+        <v>86</v>
+      </c>
+      <c r="D167" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="168" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C168" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D168" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="169" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C169" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D169" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="170" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C170" s="129">
+        <v>107</v>
+      </c>
+      <c r="D170" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="171" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C171" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D171" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="172" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C172" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D172" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="173" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C173" s="129">
+        <v>108</v>
+      </c>
+      <c r="D173" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="174" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C174" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D174" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="175" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C175" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D175" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="176" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C176" s="129">
+        <v>63</v>
+      </c>
+      <c r="D176" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="177" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C177" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D177" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="178" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C178" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D178" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="179" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C179" s="129">
+        <v>109</v>
+      </c>
+      <c r="D179" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="180" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C180" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D180" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="181" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C181" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D181" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="182" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C182" s="129">
+        <v>65</v>
+      </c>
+      <c r="D182" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="183" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C183" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D183" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="184" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C184" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D184" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="185" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C185" s="129">
+        <v>110</v>
+      </c>
+      <c r="D185" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="186" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C186" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D186" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="187" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C187" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D187" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="188" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C188" s="129">
+        <v>67</v>
+      </c>
+      <c r="D188" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="189" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C189" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D189" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="190" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C190" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D190" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="191" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C191" s="129">
+        <v>111</v>
+      </c>
+      <c r="D191" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="192" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C192" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D192" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="193" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C193" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D193" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="194" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C194" s="129">
+        <v>69</v>
+      </c>
+      <c r="D194" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="195" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C195" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D195" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="196" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C196" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D196" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="197" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C197" s="129">
+        <v>112</v>
+      </c>
+      <c r="D197" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="198" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C198" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D198" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="199" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C199" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D199" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="200" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C200" s="129">
+        <v>73</v>
+      </c>
+      <c r="D200" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="201" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C201" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D201" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="202" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C202" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D202" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="203" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C203" s="129">
+        <v>113</v>
+      </c>
+      <c r="D203" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="204" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C204" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D204" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="205" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C205" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D205" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="206" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C206" s="129">
+        <v>76</v>
+      </c>
+      <c r="D206" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="207" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C207" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D207" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="208" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C208" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D208" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="209" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C209" s="129">
+        <v>114</v>
+      </c>
+      <c r="D209" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="210" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C210" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D210" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="211" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C211" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D211" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="212" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C212" s="129">
+        <v>78</v>
+      </c>
+      <c r="D212" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="213" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C213" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D213" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="214" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C214" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D214" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="215" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C215" s="129">
+        <v>115</v>
+      </c>
+      <c r="D215" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="216" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C216" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D216" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="217" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C217" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D217" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="218" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C218" s="129">
+        <v>80</v>
+      </c>
+      <c r="D218" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="219" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C219" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D219" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="220" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C220" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D220" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="221" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C221" s="129">
+        <v>116</v>
+      </c>
+      <c r="D221" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="222" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C222" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D222" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="223" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C223" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D223" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="224" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C224" s="129">
+        <v>82</v>
+      </c>
+      <c r="D224" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="225" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C225" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D225" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="226" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C226" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D226" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="227" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C227" s="129">
+        <v>117</v>
+      </c>
+      <c r="D227" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="228" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C228" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D228" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="229" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C229" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D229" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="230" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C230" s="129">
+        <v>84</v>
+      </c>
+      <c r="D230" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="231" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C231" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D231" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="232" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C232" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D232" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="233" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C233" s="129">
+        <v>118</v>
+      </c>
+      <c r="D233" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="234" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C234" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D234" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="235" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C235" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D235" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="236" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C236" s="129">
+        <v>60</v>
+      </c>
+      <c r="D236" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="237" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C237" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D237" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="238" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C238" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D238" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="239" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C239" s="129">
+        <v>119</v>
+      </c>
+      <c r="D239" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="240" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C240" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D240" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="241" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C241" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D241" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="242" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C242" s="129">
+        <v>90</v>
+      </c>
+      <c r="D242" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="243" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C243" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D243" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="244" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C244" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D244" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="245" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C245" s="129">
+        <v>120</v>
+      </c>
+      <c r="D245" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="246" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C246" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D246" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="247" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C247" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D247" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="248" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C248" s="129">
+        <v>92</v>
+      </c>
+      <c r="D248" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="249" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C249" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D249" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="250" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C250" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D250" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="251" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C251" s="129">
+        <v>121</v>
+      </c>
+      <c r="D251" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="252" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C252" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D252" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="253" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C253" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D253" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="254" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C254" s="129">
+        <v>94</v>
+      </c>
+      <c r="D254" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="255" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C255" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D255" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="256" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C256" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D256" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="257" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C257" s="129">
+        <v>122</v>
+      </c>
+      <c r="D257" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="258" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C258" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D258" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="259" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C259" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D259" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="260" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C260" s="129">
+        <v>96</v>
+      </c>
+      <c r="D260" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="261" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C261" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D261" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="262" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C262" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D262" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="263" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C263" s="129">
+        <v>123</v>
+      </c>
+      <c r="D263" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="264" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C264" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D264" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="265" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C265" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D265" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="266" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C266" s="129">
+        <v>98</v>
+      </c>
+      <c r="D266" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="267" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C267" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D267" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="268" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C268" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D268" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="269" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C269" s="129">
+        <v>124</v>
+      </c>
+      <c r="D269" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="270" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C270" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D270" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="271" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C271" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D271" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="272" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C272" s="129">
+        <v>100</v>
+      </c>
+      <c r="D272" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="273" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C273" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D273" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="274" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C274" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D274" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="275" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C275" s="129">
+        <v>125</v>
+      </c>
+      <c r="D275" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="276" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C276" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D276" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="277" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C277" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D277" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="278" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C278" s="129">
+        <v>102</v>
+      </c>
+      <c r="D278" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="279" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C279" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D279" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="280" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C280" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D280" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="281" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C281" s="129">
+        <v>126</v>
+      </c>
+      <c r="D281" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="282" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C282" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D282" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="283" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C283" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D283" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="284" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C284" s="129">
+        <v>104</v>
+      </c>
+      <c r="D284" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="285" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C285" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D285" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="286" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C286" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D286" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="287" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C287" s="129">
+        <v>128</v>
+      </c>
+      <c r="D287" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="288" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C288" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D288" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="289" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C289" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D289" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="290" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C290" s="129">
+        <v>106</v>
+      </c>
+      <c r="D290" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="291" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C291" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D291" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="292" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C292" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D292" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="293" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C293" s="129">
+        <v>129</v>
+      </c>
+      <c r="D293" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="294" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C294" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D294" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="295" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C295" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D295" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="296" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C296" s="129">
+        <v>64</v>
+      </c>
+      <c r="D296" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="297" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C297" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D297" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="298" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C298" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D298" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="299" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C299" s="129">
+        <v>130</v>
+      </c>
+      <c r="D299" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="300" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C300" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D300" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="301" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C301" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D301" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="302" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C302" s="129">
+        <v>68</v>
+      </c>
+      <c r="D302" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="303" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C303" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D303" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="304" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C304" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D304" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="305" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C305" s="129">
+        <v>131</v>
+      </c>
+      <c r="D305" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="306" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C306" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D306" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="307" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C307" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D307" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="308" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C308" s="129">
+        <v>74</v>
+      </c>
+      <c r="D308" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="309" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C309" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D309" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="310" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C310" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D310" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="311" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C311" s="129">
+        <v>132</v>
+      </c>
+      <c r="D311" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="312" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C312" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D312" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="313" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C313" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D313" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="314" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C314" s="129">
+        <v>79</v>
+      </c>
+      <c r="D314" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="315" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C315" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D315" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="316" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C316" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D316" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="317" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C317" s="129">
+        <v>133</v>
+      </c>
+      <c r="D317" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="318" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C318" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D318" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="319" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C319" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D319" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="320" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C320" s="129">
+        <v>83</v>
+      </c>
+      <c r="D320" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="321" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C321" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D321" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="322" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C322" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D322" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="323" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C323" s="129">
+        <v>134</v>
+      </c>
+      <c r="D323" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="324" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C324" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D324" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="325" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C325" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D325" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="326" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C326" s="129">
+        <v>87</v>
+      </c>
+      <c r="D326" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="327" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C327" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D327" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="328" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C328" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D328" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="329" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C329" s="129">
+        <v>135</v>
+      </c>
+      <c r="D329" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="330" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C330" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D330" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="331" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C331" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D331" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="332" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C332" s="129">
+        <v>93</v>
+      </c>
+      <c r="D332" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="333" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C333" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D333" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="334" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C334" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D334" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="335" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C335" s="129">
+        <v>136</v>
+      </c>
+      <c r="D335" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="336" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C336" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D336" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="337" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C337" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D337" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="338" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C338" s="129">
+        <v>97</v>
+      </c>
+      <c r="D338" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="339" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C339" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D339" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="340" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C340" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D340" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="341" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C341" s="129">
         <v>137</v>
       </c>
-    </row>
-    <row r="53" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="146">
-        <v>13</v>
-      </c>
-      <c r="D53" s="145">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="54" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="147" t="s">
+      <c r="D341" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="342" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C342" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D342" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="343" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C343" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D343" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="344" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C344" s="129">
+        <v>101</v>
+      </c>
+      <c r="D344" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="345" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C345" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D345" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="346" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C346" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D346" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="347" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C347" s="129">
+        <v>138</v>
+      </c>
+      <c r="D347" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="348" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C348" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D348" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="349" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C349" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D349" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="350" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C350" s="129">
+        <v>105</v>
+      </c>
+      <c r="D350" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="351" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C351" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D351" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="352" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C352" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D352" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="353" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C353" s="129">
+        <v>139</v>
+      </c>
+      <c r="D353" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="354" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C354" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D354" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="355" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C355" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D355" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="356" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C356" s="129">
+        <v>66</v>
+      </c>
+      <c r="D356" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="357" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C357" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D357" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="358" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C358" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="D358" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="359" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C359" s="129">
+        <v>140</v>
+      </c>
+      <c r="D359" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="360" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C360" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D360" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="361" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C361" s="131" t="s">
         <v>168</v>
       </c>
-      <c r="D54" s="145">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="55" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="148" t="s">
+      <c r="D361" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="362" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C362" s="129">
+        <v>77</v>
+      </c>
+      <c r="D362" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="363" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C363" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D55" s="145">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="56" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C56" s="146">
-        <v>32</v>
-      </c>
-      <c r="D56" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="57" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="147" t="s">
+      <c r="D363" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="364" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C364" s="131" t="s">
         <v>170</v>
       </c>
-      <c r="D57" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="58" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C58" s="148" t="s">
+      <c r="D364" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="365" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C365" s="129">
+        <v>141</v>
+      </c>
+      <c r="D365" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="366" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C366" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D58" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="59" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C59" s="146">
-        <v>34</v>
-      </c>
-      <c r="D59" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="60" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C60" s="147" t="s">
+      <c r="D366" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="367" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C367" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D367" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="368" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C368" s="129">
+        <v>85</v>
+      </c>
+      <c r="D368" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="369" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C369" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D369" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="370" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C370" s="131" t="s">
         <v>170</v>
       </c>
-      <c r="D60" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="61" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C61" s="148" t="s">
+      <c r="D370" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="371" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C371" s="129">
+        <v>142</v>
+      </c>
+      <c r="D371" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="372" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C372" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D61" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="62" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C62" s="146">
-        <v>35</v>
-      </c>
-      <c r="D62" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="63" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C63" s="147" t="s">
+      <c r="D372" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="373" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C373" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D373" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="374" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C374" s="129">
+        <v>95</v>
+      </c>
+      <c r="D374" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="375" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C375" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D375" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="376" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C376" s="131" t="s">
         <v>170</v>
       </c>
-      <c r="D63" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="64" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="148" t="s">
+      <c r="D376" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="377" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C377" s="129">
+        <v>143</v>
+      </c>
+      <c r="D377" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="378" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C378" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D64" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="65" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="146">
-        <v>7</v>
-      </c>
-      <c r="D65" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="66" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="147" t="s">
+      <c r="D378" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="379" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C379" s="131" t="s">
         <v>168</v>
       </c>
-      <c r="D66" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="67" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="148" t="s">
+      <c r="D379" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="380" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C380" s="129">
+        <v>103</v>
+      </c>
+      <c r="D380" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="381" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C381" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D67" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="68" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="146">
-        <v>36</v>
-      </c>
-      <c r="D68" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="69" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="147" t="s">
+      <c r="D381" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="382" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C382" s="131" t="s">
         <v>170</v>
       </c>
-      <c r="D69" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="70" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C70" s="148" t="s">
+      <c r="D382" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="383" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C383" s="129">
+        <v>144</v>
+      </c>
+      <c r="D383" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="384" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C384" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D70" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="71" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C71" s="146">
-        <v>10</v>
-      </c>
-      <c r="D71" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="72" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="147" t="s">
+      <c r="D384" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="385" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C385" s="131" t="s">
         <v>168</v>
       </c>
-      <c r="D72" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="73" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C73" s="148" t="s">
+      <c r="D385" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="386" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C386" s="129">
+        <v>70</v>
+      </c>
+      <c r="D386" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="387" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C387" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D73" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="74" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C74" s="146">
-        <v>37</v>
-      </c>
-      <c r="D74" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="75" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C75" s="147" t="s">
+      <c r="D387" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="388" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C388" s="131" t="s">
         <v>170</v>
       </c>
-      <c r="D75" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="76" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="148" t="s">
+      <c r="D388" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="389" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C389" s="129">
+        <v>145</v>
+      </c>
+      <c r="D389" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="390" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C390" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D76" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="77" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="146">
-        <v>5</v>
-      </c>
-      <c r="D77" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="78" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C78" s="147" t="s">
+      <c r="D390" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="391" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C391" s="131" t="s">
         <v>168</v>
       </c>
-      <c r="D78" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="79" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C79" s="148" t="s">
+      <c r="D391" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="392" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C392" s="129">
+        <v>91</v>
+      </c>
+      <c r="D392" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="393" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C393" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D79" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="80" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C80" s="146">
-        <v>38</v>
-      </c>
-      <c r="D80" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="81" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="147" t="s">
+      <c r="D393" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="394" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C394" s="131" t="s">
         <v>170</v>
       </c>
-      <c r="D81" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="82" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C82" s="148" t="s">
+      <c r="D394" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="395" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C395" s="129">
+        <v>146</v>
+      </c>
+      <c r="D395" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="396" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C396" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D82" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="83" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C83" s="146">
-        <v>20</v>
-      </c>
-      <c r="D83" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="84" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C84" s="147" t="s">
+      <c r="D396" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="397" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C397" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D397" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="398" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C398" s="129">
+        <v>62</v>
+      </c>
+      <c r="D398" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="399" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C399" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D399" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="400" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C400" s="131" t="s">
         <v>170</v>
       </c>
-      <c r="D84" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="85" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C85" s="148" t="s">
+      <c r="D400" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="401" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C401" s="129">
+        <v>147</v>
+      </c>
+      <c r="D401" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="402" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C402" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D85" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="86" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C86" s="146">
-        <v>39</v>
-      </c>
-      <c r="D86" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="87" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C87" s="147" t="s">
+      <c r="D402" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="403" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C403" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D403" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="404" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C404" s="129">
+        <v>99</v>
+      </c>
+      <c r="D404" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="405" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C405" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D405" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="406" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C406" s="131" t="s">
         <v>170</v>
       </c>
-      <c r="D87" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="88" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C88" s="148" t="s">
+      <c r="D406" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="407" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C407" s="129">
+        <v>148</v>
+      </c>
+      <c r="D407" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="408" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C408" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D88" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="89" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C89" s="146">
-        <v>24</v>
-      </c>
-      <c r="D89" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="90" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C90" s="147" t="s">
+      <c r="D408" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="409" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C409" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="D409" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="410" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C410" s="129">
+        <v>81</v>
+      </c>
+      <c r="D410" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="411" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C411" s="130" t="s">
+        <v>169</v>
+      </c>
+      <c r="D411" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="412" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C412" s="131" t="s">
         <v>170</v>
       </c>
-      <c r="D90" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="91" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C91" s="148" t="s">
+      <c r="D412" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="413" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C413" s="129">
+        <v>149</v>
+      </c>
+      <c r="D413" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="414" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C414" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="D91" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="92" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C92" s="146">
-        <v>40</v>
-      </c>
-      <c r="D92" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="93" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C93" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D93" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="94" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C94" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D94" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="95" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C95" s="146">
-        <v>26</v>
-      </c>
-      <c r="D95" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="96" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C96" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D96" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="97" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C97" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D97" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="98" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="146">
-        <v>41</v>
-      </c>
-      <c r="D98" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="99" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C99" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D99" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="100" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C100" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D100" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="101" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C101" s="146">
-        <v>28</v>
-      </c>
-      <c r="D101" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="102" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C102" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D102" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="103" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C103" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D103" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="104" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C104" s="146">
-        <v>43</v>
-      </c>
-      <c r="D104" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="105" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C105" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D105" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="106" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C106" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D106" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="107" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C107" s="146">
-        <v>31</v>
-      </c>
-      <c r="D107" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="108" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D108" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="109" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C109" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D109" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="110" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C110" s="146">
-        <v>44</v>
-      </c>
-      <c r="D110" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="111" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C111" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D111" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="112" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C112" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D112" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="113" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C113" s="146">
-        <v>6</v>
-      </c>
-      <c r="D113" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="114" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C114" s="147" t="s">
+      <c r="D414" s="128">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="415" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C415" s="131" t="s">
         <v>168</v>
       </c>
-      <c r="D114" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="115" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C115" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D115" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="116" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C116" s="146">
-        <v>45</v>
-      </c>
-      <c r="D116" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="117" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C117" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D117" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="118" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C118" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D118" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="119" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C119" s="146">
-        <v>11</v>
-      </c>
-      <c r="D119" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="120" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C120" s="147" t="s">
-        <v>168</v>
-      </c>
-      <c r="D120" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="121" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C121" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D121" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="122" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C122" s="146">
-        <v>46</v>
-      </c>
-      <c r="D122" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="123" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C123" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D123" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="124" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C124" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D124" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="125" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C125" s="146">
-        <v>23</v>
-      </c>
-      <c r="D125" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="126" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C126" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D126" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="127" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C127" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D127" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="128" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C128" s="146">
-        <v>47</v>
-      </c>
-      <c r="D128" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="129" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C129" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D129" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="130" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C130" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D130" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="131" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C131" s="146">
-        <v>27</v>
-      </c>
-      <c r="D131" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="132" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C132" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D132" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="133" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C133" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D133" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="134" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C134" s="146">
-        <v>48</v>
-      </c>
-      <c r="D134" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="135" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D135" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="136" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D136" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="137" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C137" s="146">
-        <v>4</v>
-      </c>
-      <c r="D137" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="138" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C138" s="147" t="s">
-        <v>168</v>
-      </c>
-      <c r="D138" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="139" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C139" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D139" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="140" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C140" s="146">
-        <v>49</v>
-      </c>
-      <c r="D140" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="141" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C141" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D141" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="142" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C142" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D142" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="143" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C143" s="146">
-        <v>19</v>
-      </c>
-      <c r="D143" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="144" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C144" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D144" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="145" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C145" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D145" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="146" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C146" s="146">
-        <v>50</v>
-      </c>
-      <c r="D146" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="147" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C147" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D147" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="148" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C148" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D148" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="149" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C149" s="146">
-        <v>29</v>
-      </c>
-      <c r="D149" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="150" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C150" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D150" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="151" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D151" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="152" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="146">
-        <v>51</v>
-      </c>
-      <c r="D152" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="153" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D153" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="154" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D154" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="155" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C155" s="146">
-        <v>25</v>
-      </c>
-      <c r="D155" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="156" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C156" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D156" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="157" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C157" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D157" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="158" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C158" s="146">
-        <v>52</v>
-      </c>
-      <c r="D158" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="159" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C159" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D159" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="160" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C160" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D160" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="161" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C161" s="146">
-        <v>9</v>
-      </c>
-      <c r="D161" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="162" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C162" s="147" t="s">
-        <v>168</v>
-      </c>
-      <c r="D162" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="163" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C163" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D163" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="164" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C164" s="146">
-        <v>54</v>
-      </c>
-      <c r="D164" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="165" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C165" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D165" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="166" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C166" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D166" s="145">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="167" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C167" s="146">
-        <v>86</v>
-      </c>
-      <c r="D167" s="145">
+      <c r="D415" s="128">
         <v>400</v>
       </c>
     </row>
-    <row r="168" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C168" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D168" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="169" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C169" s="148" t="s">
+    <row r="416" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C416" s="129" t="s">
         <v>171</v>
       </c>
-      <c r="D169" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="170" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C170" s="146">
-        <v>107</v>
-      </c>
-      <c r="D170" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="171" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C171" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D171" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="172" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C172" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D172" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="173" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C173" s="146">
-        <v>108</v>
-      </c>
-      <c r="D173" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="174" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C174" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D174" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="175" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C175" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D175" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="176" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C176" s="146">
-        <v>63</v>
-      </c>
-      <c r="D176" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="177" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C177" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D177" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="178" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C178" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D178" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="179" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C179" s="146">
-        <v>109</v>
-      </c>
-      <c r="D179" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="180" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C180" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D180" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="181" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C181" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D181" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="182" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C182" s="146">
-        <v>65</v>
-      </c>
-      <c r="D182" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="183" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C183" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D183" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="184" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C184" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D184" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="185" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C185" s="146">
-        <v>110</v>
-      </c>
-      <c r="D185" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="186" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C186" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D186" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="187" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C187" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D187" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="188" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C188" s="146">
-        <v>67</v>
-      </c>
-      <c r="D188" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="189" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C189" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D189" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="190" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C190" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D190" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="191" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C191" s="146">
-        <v>111</v>
-      </c>
-      <c r="D191" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="192" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C192" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D192" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="193" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C193" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D193" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="194" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C194" s="146">
-        <v>69</v>
-      </c>
-      <c r="D194" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="195" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C195" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D195" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="196" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C196" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D196" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="197" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C197" s="146">
-        <v>112</v>
-      </c>
-      <c r="D197" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="198" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C198" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D198" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="199" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C199" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D199" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="200" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C200" s="146">
-        <v>73</v>
-      </c>
-      <c r="D200" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="201" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C201" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D201" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="202" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C202" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D202" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="203" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C203" s="146">
-        <v>113</v>
-      </c>
-      <c r="D203" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="204" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C204" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D204" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="205" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C205" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D205" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="206" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C206" s="146">
-        <v>76</v>
-      </c>
-      <c r="D206" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="207" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C207" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D207" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="208" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C208" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D208" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="209" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C209" s="146">
-        <v>114</v>
-      </c>
-      <c r="D209" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="210" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C210" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D210" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="211" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C211" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D211" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="212" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C212" s="146">
-        <v>78</v>
-      </c>
-      <c r="D212" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="213" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C213" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D213" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="214" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C214" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D214" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="215" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C215" s="146">
-        <v>115</v>
-      </c>
-      <c r="D215" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="216" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C216" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D216" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="217" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C217" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D217" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="218" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C218" s="146">
-        <v>80</v>
-      </c>
-      <c r="D218" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="219" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C219" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D219" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="220" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C220" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D220" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="221" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C221" s="146">
-        <v>116</v>
-      </c>
-      <c r="D221" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="222" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C222" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D222" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="223" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C223" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D223" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="224" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C224" s="146">
-        <v>82</v>
-      </c>
-      <c r="D224" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="225" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C225" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D225" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="226" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C226" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D226" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="227" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C227" s="146">
-        <v>117</v>
-      </c>
-      <c r="D227" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="228" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C228" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D228" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="229" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C229" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D229" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="230" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C230" s="146">
-        <v>84</v>
-      </c>
-      <c r="D230" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="231" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C231" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D231" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="232" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C232" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D232" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="233" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C233" s="146">
-        <v>118</v>
-      </c>
-      <c r="D233" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="234" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C234" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D234" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="235" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C235" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D235" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="236" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C236" s="146">
-        <v>60</v>
-      </c>
-      <c r="D236" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="237" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C237" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D237" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="238" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C238" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D238" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="239" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C239" s="146">
-        <v>119</v>
-      </c>
-      <c r="D239" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="240" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C240" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D240" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="241" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C241" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D241" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="242" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C242" s="146">
-        <v>90</v>
-      </c>
-      <c r="D242" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="243" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C243" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D243" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="244" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C244" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D244" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="245" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C245" s="146">
-        <v>120</v>
-      </c>
-      <c r="D245" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="246" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C246" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D246" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="247" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C247" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D247" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="248" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C248" s="146">
-        <v>92</v>
-      </c>
-      <c r="D248" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="249" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C249" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D249" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="250" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C250" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D250" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="251" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C251" s="146">
-        <v>121</v>
-      </c>
-      <c r="D251" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="252" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C252" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D252" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="253" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C253" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D253" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="254" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C254" s="146">
-        <v>94</v>
-      </c>
-      <c r="D254" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="255" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C255" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D255" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="256" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C256" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D256" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="257" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C257" s="146">
-        <v>122</v>
-      </c>
-      <c r="D257" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="258" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C258" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D258" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="259" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C259" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D259" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="260" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C260" s="146">
-        <v>96</v>
-      </c>
-      <c r="D260" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="261" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C261" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D261" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="262" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C262" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D262" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="263" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C263" s="146">
-        <v>123</v>
-      </c>
-      <c r="D263" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="264" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C264" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D264" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="265" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C265" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D265" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="266" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C266" s="146">
-        <v>98</v>
-      </c>
-      <c r="D266" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="267" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C267" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D267" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="268" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C268" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D268" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="269" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C269" s="146">
-        <v>124</v>
-      </c>
-      <c r="D269" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="270" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C270" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D270" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="271" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C271" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D271" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="272" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C272" s="146">
-        <v>100</v>
-      </c>
-      <c r="D272" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="273" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C273" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D273" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="274" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C274" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D274" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="275" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C275" s="146">
-        <v>125</v>
-      </c>
-      <c r="D275" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="276" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C276" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D276" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="277" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C277" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D277" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="278" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C278" s="146">
-        <v>102</v>
-      </c>
-      <c r="D278" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="279" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C279" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D279" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="280" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C280" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D280" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="281" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C281" s="146">
-        <v>126</v>
-      </c>
-      <c r="D281" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="282" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C282" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D282" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="283" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C283" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D283" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="284" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C284" s="146">
-        <v>104</v>
-      </c>
-      <c r="D284" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="285" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C285" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D285" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="286" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C286" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D286" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="287" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C287" s="146">
-        <v>128</v>
-      </c>
-      <c r="D287" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="288" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C288" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D288" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="289" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C289" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D289" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="290" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C290" s="146">
-        <v>106</v>
-      </c>
-      <c r="D290" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="291" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C291" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D291" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="292" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C292" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D292" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="293" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C293" s="146">
-        <v>129</v>
-      </c>
-      <c r="D293" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="294" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C294" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D294" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="295" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C295" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D295" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="296" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C296" s="146">
-        <v>64</v>
-      </c>
-      <c r="D296" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="297" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C297" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D297" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="298" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C298" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D298" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="299" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C299" s="146">
-        <v>130</v>
-      </c>
-      <c r="D299" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="300" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C300" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D300" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="301" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C301" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D301" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="302" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C302" s="146">
-        <v>68</v>
-      </c>
-      <c r="D302" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="303" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C303" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D303" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="304" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C304" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D304" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="305" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C305" s="146">
-        <v>131</v>
-      </c>
-      <c r="D305" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="306" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C306" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D306" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="307" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C307" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D307" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="308" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C308" s="146">
-        <v>74</v>
-      </c>
-      <c r="D308" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="309" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C309" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D309" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="310" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C310" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D310" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="311" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C311" s="146">
-        <v>132</v>
-      </c>
-      <c r="D311" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="312" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C312" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D312" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="313" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C313" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D313" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="314" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C314" s="146">
-        <v>79</v>
-      </c>
-      <c r="D314" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="315" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C315" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D315" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="316" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C316" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D316" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="317" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C317" s="146">
-        <v>133</v>
-      </c>
-      <c r="D317" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="318" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C318" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D318" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="319" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C319" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D319" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="320" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C320" s="146">
-        <v>83</v>
-      </c>
-      <c r="D320" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="321" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C321" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D321" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="322" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C322" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D322" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="323" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C323" s="146">
-        <v>134</v>
-      </c>
-      <c r="D323" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="324" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C324" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D324" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="325" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C325" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D325" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="326" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C326" s="146">
-        <v>87</v>
-      </c>
-      <c r="D326" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="327" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C327" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D327" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="328" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C328" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D328" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="329" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C329" s="146">
-        <v>135</v>
-      </c>
-      <c r="D329" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="330" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C330" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D330" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="331" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C331" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D331" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="332" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C332" s="146">
-        <v>93</v>
-      </c>
-      <c r="D332" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="333" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C333" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D333" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="334" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C334" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D334" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="335" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C335" s="146">
-        <v>136</v>
-      </c>
-      <c r="D335" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="336" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C336" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D336" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="337" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C337" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D337" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="338" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C338" s="146">
-        <v>97</v>
-      </c>
-      <c r="D338" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="339" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C339" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D339" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="340" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C340" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D340" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="341" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C341" s="146">
-        <v>137</v>
-      </c>
-      <c r="D341" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="342" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C342" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D342" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="343" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C343" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D343" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="344" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C344" s="146">
-        <v>101</v>
-      </c>
-      <c r="D344" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="345" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C345" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D345" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="346" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C346" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D346" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="347" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C347" s="146">
-        <v>138</v>
-      </c>
-      <c r="D347" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="348" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C348" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D348" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="349" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C349" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D349" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="350" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C350" s="146">
-        <v>105</v>
-      </c>
-      <c r="D350" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="351" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C351" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D351" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="352" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C352" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D352" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="353" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C353" s="146">
-        <v>139</v>
-      </c>
-      <c r="D353" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="354" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C354" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D354" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="355" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C355" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D355" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="356" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C356" s="146">
-        <v>66</v>
-      </c>
-      <c r="D356" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="357" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C357" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D357" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="358" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C358" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D358" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="359" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C359" s="146">
-        <v>140</v>
-      </c>
-      <c r="D359" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="360" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C360" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D360" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="361" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C361" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D361" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="362" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C362" s="146">
-        <v>77</v>
-      </c>
-      <c r="D362" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="363" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C363" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D363" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="364" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C364" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D364" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="365" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C365" s="146">
-        <v>141</v>
-      </c>
-      <c r="D365" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="366" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C366" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D366" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="367" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C367" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D367" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="368" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C368" s="146">
-        <v>85</v>
-      </c>
-      <c r="D368" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="369" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C369" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D369" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="370" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C370" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D370" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="371" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C371" s="146">
-        <v>142</v>
-      </c>
-      <c r="D371" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="372" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C372" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D372" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="373" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C373" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D373" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="374" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C374" s="146">
-        <v>95</v>
-      </c>
-      <c r="D374" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="375" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C375" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D375" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="376" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C376" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D376" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="377" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C377" s="146">
-        <v>143</v>
-      </c>
-      <c r="D377" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="378" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C378" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D378" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="379" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C379" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D379" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="380" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C380" s="146">
-        <v>103</v>
-      </c>
-      <c r="D380" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="381" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C381" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D381" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="382" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C382" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D382" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="383" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C383" s="146">
-        <v>144</v>
-      </c>
-      <c r="D383" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="384" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C384" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D384" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="385" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C385" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D385" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="386" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C386" s="146">
-        <v>70</v>
-      </c>
-      <c r="D386" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="387" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C387" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D387" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="388" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C388" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D388" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="389" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C389" s="146">
-        <v>145</v>
-      </c>
-      <c r="D389" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="390" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C390" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D390" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="391" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C391" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D391" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="392" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C392" s="146">
-        <v>91</v>
-      </c>
-      <c r="D392" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="393" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C393" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D393" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="394" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C394" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D394" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="395" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C395" s="146">
-        <v>146</v>
-      </c>
-      <c r="D395" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="396" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C396" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D396" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="397" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C397" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D397" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="398" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C398" s="146">
-        <v>62</v>
-      </c>
-      <c r="D398" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="399" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C399" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D399" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="400" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C400" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D400" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="401" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C401" s="146">
-        <v>147</v>
-      </c>
-      <c r="D401" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="402" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C402" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D402" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="403" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C403" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D403" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="404" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C404" s="146">
-        <v>99</v>
-      </c>
-      <c r="D404" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="405" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C405" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D405" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="406" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C406" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D406" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="407" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C407" s="146">
-        <v>148</v>
-      </c>
-      <c r="D407" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="408" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C408" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D408" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="409" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C409" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D409" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="410" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C410" s="146">
-        <v>81</v>
-      </c>
-      <c r="D410" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="411" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C411" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D411" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="412" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C412" s="148" t="s">
-        <v>171</v>
-      </c>
-      <c r="D412" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="413" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C413" s="146">
-        <v>149</v>
-      </c>
-      <c r="D413" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="414" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C414" s="147" t="s">
-        <v>170</v>
-      </c>
-      <c r="D414" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="415" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C415" s="148" t="s">
-        <v>169</v>
-      </c>
-      <c r="D415" s="145">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="416" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C416" s="146" t="s">
-        <v>172</v>
-      </c>
-      <c r="D416" s="145">
+      <c r="D416" s="128">
         <v>320</v>
       </c>
     </row>

--- a/maestra.xlsx
+++ b/maestra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\cotizador-web-mp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9000A0CA-3498-4E16-AEED-871BD437A169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812F7C67-C5FD-44BA-A2EB-14E02DB79E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{192F143D-BAEC-4662-86EC-0FD2BF508275}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{192F143D-BAEC-4662-86EC-0FD2BF508275}"/>
   </bookViews>
   <sheets>
     <sheet name="Condiciones Comerciales" sheetId="1" r:id="rId1"/>
@@ -1526,7 +1526,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1878,30 +1878,6 @@
     <xf numFmtId="167" fontId="35" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1933,10 +1909,30 @@
     <xf numFmtId="167" fontId="35" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency [0]" xfId="1" builtinId="7"/>
@@ -66841,28 +66837,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="Q1" s="141" t="s">
+      <c r="Q1" s="155" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
-      <c r="V1" s="141"/>
-      <c r="W1" s="141"/>
+      <c r="R1" s="155"/>
+      <c r="S1" s="155"/>
+      <c r="T1" s="155"/>
+      <c r="U1" s="155"/>
+      <c r="V1" s="155"/>
+      <c r="W1" s="155"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="141"/>
-      <c r="S2" s="141"/>
-      <c r="T2" s="141"/>
-      <c r="U2" s="141"/>
-      <c r="V2" s="141"/>
-      <c r="W2" s="141"/>
+      <c r="Q2" s="155"/>
+      <c r="R2" s="155"/>
+      <c r="S2" s="155"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="155"/>
     </row>
     <row r="3" spans="1:29" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
@@ -66958,18 +66954,18 @@
         <v>20</v>
       </c>
       <c r="P4" s="25"/>
-      <c r="Q4" s="137" t="s">
+      <c r="Q4" s="152" t="s">
         <v>21</v>
       </c>
-      <c r="R4" s="137"/>
+      <c r="R4" s="152"/>
       <c r="S4" s="26"/>
       <c r="T4" s="27"/>
       <c r="U4" s="28"/>
-      <c r="V4" s="137" t="s">
+      <c r="V4" s="152" t="s">
         <v>22</v>
       </c>
-      <c r="W4" s="137"/>
-      <c r="X4" s="142"/>
+      <c r="W4" s="152"/>
+      <c r="X4" s="156"/>
       <c r="AA4" s="29" t="s">
         <v>23</v>
       </c>
@@ -67977,20 +67973,20 @@
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B23" s="143" t="s">
+      <c r="B23" s="157" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="143"/>
-      <c r="D23" s="143"/>
-      <c r="E23" s="143"/>
-      <c r="F23" s="143"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="143"/>
-      <c r="I23" s="143"/>
-      <c r="J23" s="143"/>
-      <c r="K23" s="143"/>
-      <c r="L23" s="143"/>
-      <c r="M23" s="143"/>
+      <c r="C23" s="157"/>
+      <c r="D23" s="157"/>
+      <c r="E23" s="157"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="157"/>
+      <c r="H23" s="157"/>
+      <c r="I23" s="157"/>
+      <c r="J23" s="157"/>
+      <c r="K23" s="157"/>
+      <c r="L23" s="157"/>
+      <c r="M23" s="157"/>
       <c r="N23" s="71"/>
       <c r="R23" s="69" t="s">
         <v>106</v>
@@ -68000,20 +67996,20 @@
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B24" s="139" t="s">
+      <c r="B24" s="153" t="s">
         <v>108</v>
       </c>
-      <c r="C24" s="139"/>
-      <c r="D24" s="139"/>
-      <c r="E24" s="139"/>
-      <c r="F24" s="139"/>
-      <c r="G24" s="139"/>
-      <c r="H24" s="139"/>
-      <c r="I24" s="139"/>
-      <c r="J24" s="139"/>
-      <c r="K24" s="139"/>
-      <c r="L24" s="139"/>
-      <c r="M24" s="139"/>
+      <c r="C24" s="153"/>
+      <c r="D24" s="153"/>
+      <c r="E24" s="153"/>
+      <c r="F24" s="153"/>
+      <c r="G24" s="153"/>
+      <c r="H24" s="153"/>
+      <c r="I24" s="153"/>
+      <c r="J24" s="153"/>
+      <c r="K24" s="153"/>
+      <c r="L24" s="153"/>
+      <c r="M24" s="153"/>
       <c r="R24" s="70" t="s">
         <v>109</v>
       </c>
@@ -68022,38 +68018,38 @@
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B25" s="139" t="s">
+      <c r="B25" s="153" t="s">
         <v>111</v>
       </c>
-      <c r="C25" s="139"/>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
-      <c r="G25" s="139"/>
-      <c r="H25" s="139"/>
-      <c r="I25" s="139"/>
-      <c r="J25" s="139"/>
-      <c r="K25" s="139"/>
-      <c r="L25" s="139"/>
-      <c r="M25" s="139"/>
-      <c r="V25" s="144"/>
-      <c r="W25" s="144"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="153"/>
+      <c r="H25" s="153"/>
+      <c r="I25" s="153"/>
+      <c r="J25" s="153"/>
+      <c r="K25" s="153"/>
+      <c r="L25" s="153"/>
+      <c r="M25" s="153"/>
+      <c r="V25" s="154"/>
+      <c r="W25" s="154"/>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B26" s="139" t="s">
+      <c r="B26" s="153" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="139"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="139"/>
-      <c r="I26" s="139"/>
-      <c r="J26" s="139"/>
-      <c r="K26" s="139"/>
-      <c r="L26" s="139"/>
-      <c r="M26" s="139"/>
+      <c r="C26" s="153"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="153"/>
+      <c r="F26" s="153"/>
+      <c r="G26" s="153"/>
+      <c r="H26" s="153"/>
+      <c r="I26" s="153"/>
+      <c r="J26" s="153"/>
+      <c r="K26" s="153"/>
+      <c r="L26" s="153"/>
+      <c r="M26" s="153"/>
       <c r="N26" s="73"/>
       <c r="R26" s="69" t="s">
         <v>113</v>
@@ -68063,20 +68059,20 @@
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B27" s="139" t="s">
+      <c r="B27" s="153" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="139"/>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="139"/>
-      <c r="G27" s="139"/>
-      <c r="H27" s="139"/>
-      <c r="I27" s="139"/>
-      <c r="J27" s="139"/>
-      <c r="K27" s="139"/>
-      <c r="L27" s="139"/>
-      <c r="M27" s="139"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="153"/>
+      <c r="F27" s="153"/>
+      <c r="G27" s="153"/>
+      <c r="H27" s="153"/>
+      <c r="I27" s="153"/>
+      <c r="J27" s="153"/>
+      <c r="K27" s="153"/>
+      <c r="L27" s="153"/>
+      <c r="M27" s="153"/>
       <c r="N27" s="73"/>
       <c r="R27" s="1" t="s">
         <v>116</v>
@@ -68086,20 +68082,20 @@
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B28" s="139" t="s">
+      <c r="B28" s="153" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="139"/>
-      <c r="D28" s="139"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
-      <c r="G28" s="139"/>
-      <c r="H28" s="139"/>
-      <c r="I28" s="139"/>
-      <c r="J28" s="139"/>
-      <c r="K28" s="139"/>
-      <c r="L28" s="139"/>
-      <c r="M28" s="139"/>
+      <c r="C28" s="153"/>
+      <c r="D28" s="153"/>
+      <c r="E28" s="153"/>
+      <c r="F28" s="153"/>
+      <c r="G28" s="153"/>
+      <c r="H28" s="153"/>
+      <c r="I28" s="153"/>
+      <c r="J28" s="153"/>
+      <c r="K28" s="153"/>
+      <c r="L28" s="153"/>
+      <c r="M28" s="153"/>
       <c r="N28" s="73"/>
       <c r="R28" s="1" t="s">
         <v>119</v>
@@ -68109,20 +68105,20 @@
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B29" s="139" t="s">
+      <c r="B29" s="153" t="s">
         <v>121</v>
       </c>
-      <c r="C29" s="139"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
-      <c r="H29" s="139"/>
-      <c r="I29" s="139"/>
-      <c r="J29" s="139"/>
-      <c r="K29" s="139"/>
-      <c r="L29" s="139"/>
-      <c r="M29" s="139"/>
+      <c r="C29" s="153"/>
+      <c r="D29" s="153"/>
+      <c r="E29" s="153"/>
+      <c r="F29" s="153"/>
+      <c r="G29" s="153"/>
+      <c r="H29" s="153"/>
+      <c r="I29" s="153"/>
+      <c r="J29" s="153"/>
+      <c r="K29" s="153"/>
+      <c r="L29" s="153"/>
+      <c r="M29" s="153"/>
       <c r="R29" s="1" t="s">
         <v>122</v>
       </c>
@@ -68131,20 +68127,20 @@
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B30" s="138" t="s">
+      <c r="B30" s="158" t="s">
         <v>124</v>
       </c>
-      <c r="C30" s="138"/>
-      <c r="D30" s="138"/>
-      <c r="E30" s="138"/>
-      <c r="F30" s="138"/>
-      <c r="G30" s="138"/>
-      <c r="H30" s="138"/>
-      <c r="I30" s="138"/>
-      <c r="J30" s="138"/>
-      <c r="K30" s="138"/>
-      <c r="L30" s="138"/>
-      <c r="M30" s="138"/>
+      <c r="C30" s="158"/>
+      <c r="D30" s="158"/>
+      <c r="E30" s="158"/>
+      <c r="F30" s="158"/>
+      <c r="G30" s="158"/>
+      <c r="H30" s="158"/>
+      <c r="I30" s="158"/>
+      <c r="J30" s="158"/>
+      <c r="K30" s="158"/>
+      <c r="L30" s="158"/>
+      <c r="M30" s="158"/>
       <c r="R30" s="1" t="s">
         <v>125</v>
       </c>
@@ -68153,20 +68149,20 @@
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B31" s="138" t="s">
+      <c r="B31" s="158" t="s">
         <v>127</v>
       </c>
-      <c r="C31" s="138"/>
-      <c r="D31" s="138"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="138"/>
-      <c r="G31" s="138"/>
-      <c r="H31" s="138"/>
-      <c r="I31" s="138"/>
-      <c r="J31" s="138"/>
-      <c r="K31" s="138"/>
-      <c r="L31" s="138"/>
-      <c r="M31" s="138"/>
+      <c r="C31" s="158"/>
+      <c r="D31" s="158"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="158"/>
+      <c r="G31" s="158"/>
+      <c r="H31" s="158"/>
+      <c r="I31" s="158"/>
+      <c r="J31" s="158"/>
+      <c r="K31" s="158"/>
+      <c r="L31" s="158"/>
+      <c r="M31" s="158"/>
       <c r="R31" s="70" t="s">
         <v>128</v>
       </c>
@@ -68175,36 +68171,36 @@
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B32" s="138" t="s">
+      <c r="B32" s="158" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="138"/>
-      <c r="D32" s="138"/>
-      <c r="E32" s="138"/>
-      <c r="F32" s="138"/>
-      <c r="G32" s="138"/>
-      <c r="H32" s="138"/>
-      <c r="I32" s="138"/>
-      <c r="J32" s="138"/>
-      <c r="K32" s="138"/>
-      <c r="L32" s="138"/>
-      <c r="M32" s="138"/>
+      <c r="C32" s="158"/>
+      <c r="D32" s="158"/>
+      <c r="E32" s="158"/>
+      <c r="F32" s="158"/>
+      <c r="G32" s="158"/>
+      <c r="H32" s="158"/>
+      <c r="I32" s="158"/>
+      <c r="J32" s="158"/>
+      <c r="K32" s="158"/>
+      <c r="L32" s="158"/>
+      <c r="M32" s="158"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B33" s="139" t="s">
+      <c r="B33" s="153" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="139"/>
-      <c r="D33" s="139"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
-      <c r="G33" s="139"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
-      <c r="J33" s="139"/>
-      <c r="K33" s="139"/>
-      <c r="L33" s="139"/>
-      <c r="M33" s="139"/>
+      <c r="C33" s="153"/>
+      <c r="D33" s="153"/>
+      <c r="E33" s="153"/>
+      <c r="F33" s="153"/>
+      <c r="G33" s="153"/>
+      <c r="H33" s="153"/>
+      <c r="I33" s="153"/>
+      <c r="J33" s="153"/>
+      <c r="K33" s="153"/>
+      <c r="L33" s="153"/>
+      <c r="M33" s="153"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="74"/>
@@ -68286,9 +68282,9 @@
       <c r="B42" s="69"/>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B43" s="140"/>
-      <c r="C43" s="140"/>
-      <c r="D43" s="140"/>
+      <c r="B43" s="159"/>
+      <c r="C43" s="159"/>
+      <c r="D43" s="159"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:M21" xr:uid="{27C47C64-5BA2-4774-BE4B-59B66BC9B742}">
@@ -68315,13 +68311,6 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="16">
-    <mergeCell ref="B25:M25"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="Q1:W2"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="B24:M24"/>
     <mergeCell ref="B32:M32"/>
     <mergeCell ref="B33:M33"/>
     <mergeCell ref="B43:D43"/>
@@ -68331,6 +68320,13 @@
     <mergeCell ref="B29:M29"/>
     <mergeCell ref="B30:M30"/>
     <mergeCell ref="B31:M31"/>
+    <mergeCell ref="B25:M25"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="Q1:W2"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="V4:X4"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="B24:M24"/>
   </mergeCells>
   <conditionalFormatting sqref="T4 X4 T6:T17 X6:X19">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="VB">
@@ -68378,13 +68374,13 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="137" t="s">
+      <c r="C4" s="152" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="152"/>
+      <c r="G4" s="152"/>
     </row>
     <row r="5" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C5" s="79"/>
@@ -68475,7 +68471,7 @@
     </row>
     <row r="15" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="25"/>
-      <c r="C15" s="145" t="s">
+      <c r="C15" s="137" t="s">
         <v>141</v>
       </c>
       <c r="D15" s="91">
@@ -68502,10 +68498,10 @@
     </row>
     <row r="18" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="25"/>
-      <c r="C18" s="146" t="s">
+      <c r="C18" s="138" t="s">
         <v>143</v>
       </c>
-      <c r="D18" s="147">
+      <c r="D18" s="139">
         <f>D10*(100%-D15)</f>
         <v>2887.53</v>
       </c>
@@ -68513,10 +68509,10 @@
     </row>
     <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="25"/>
-      <c r="C19" s="146" t="s">
+      <c r="C19" s="138" t="s">
         <v>144</v>
       </c>
-      <c r="D19" s="147">
+      <c r="D19" s="139">
         <f>D11</f>
         <v>350</v>
       </c>
@@ -68527,10 +68523,10 @@
     </row>
     <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="25"/>
-      <c r="C20" s="146" t="s">
+      <c r="C20" s="138" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="147">
+      <c r="D20" s="139">
         <f>D12</f>
         <v>80</v>
       </c>
@@ -68540,10 +68536,10 @@
     </row>
     <row r="21" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="25"/>
-      <c r="C21" s="148" t="s">
+      <c r="C21" s="140" t="s">
         <v>145</v>
       </c>
-      <c r="D21" s="149">
+      <c r="D21" s="141">
         <f>SUM(D18:D20)</f>
         <v>3317.53</v>
       </c>
@@ -68561,10 +68557,10 @@
     </row>
     <row r="23" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="25"/>
-      <c r="C23" s="150" t="s">
+      <c r="C23" s="142" t="s">
         <v>147</v>
       </c>
-      <c r="D23" s="151">
+      <c r="D23" s="143">
         <v>0.1</v>
       </c>
       <c r="F23" s="86"/>
@@ -68583,10 +68579,10 @@
     </row>
     <row r="25" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="25"/>
-      <c r="C25" s="152" t="s">
+      <c r="C25" s="144" t="s">
         <v>149</v>
       </c>
-      <c r="D25" s="153">
+      <c r="D25" s="145">
         <f>100000/H23</f>
         <v>2.512437823444964</v>
       </c>
@@ -68600,10 +68596,10 @@
     </row>
     <row r="26" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="25"/>
-      <c r="C26" s="154" t="s">
+      <c r="C26" s="146" t="s">
         <v>150</v>
       </c>
-      <c r="D26" s="151">
+      <c r="D26" s="143">
         <v>0.02</v>
       </c>
       <c r="E26" s="98"/>
@@ -68613,10 +68609,10 @@
     </row>
     <row r="27" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="25"/>
-      <c r="C27" s="152" t="s">
+      <c r="C27" s="144" t="s">
         <v>151</v>
       </c>
-      <c r="D27" s="155">
+      <c r="D27" s="147">
         <f>D21*D26</f>
         <v>66.3506</v>
       </c>
@@ -68630,10 +68626,10 @@
     </row>
     <row r="28" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="25"/>
-      <c r="C28" s="156" t="s">
+      <c r="C28" s="148" t="s">
         <v>152</v>
       </c>
-      <c r="D28" s="155">
+      <c r="D28" s="147">
         <f>IF(D23=0%,0,D21*D23-D25-D27)</f>
         <v>262.88996217655512</v>
       </c>
@@ -68748,10 +68744,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="25"/>
-      <c r="C35" s="160" t="s">
+      <c r="C35" s="149" t="s">
         <v>155</v>
       </c>
-      <c r="D35" s="161">
+      <c r="D35" s="150">
         <f>D29/D33</f>
         <v>3732.2212500000001</v>
       </c>
@@ -68774,14 +68770,14 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="25"/>
-      <c r="C37" s="157" t="s">
+      <c r="C37" s="149" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="158">
+      <c r="D37" s="150">
         <f>D25+D27+D28</f>
         <v>331.7530000000001</v>
       </c>
-      <c r="E37" s="159">
+      <c r="E37" s="151">
         <f t="shared" ref="E37:E38" si="0">D37/$D$35</f>
         <v>8.888888888888892E-2</v>
       </c>
@@ -68789,14 +68785,14 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="25"/>
-      <c r="C38" s="157" t="s">
+      <c r="C38" s="149" t="s">
         <v>174</v>
       </c>
-      <c r="D38" s="158">
+      <c r="D38" s="150">
         <f>D35*D33</f>
         <v>2985.777</v>
       </c>
-      <c r="E38" s="159">
+      <c r="E38" s="151">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>

--- a/maestra.xlsx
+++ b/maestra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\cotizador-web-mp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812F7C67-C5FD-44BA-A2EB-14E02DB79E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33978A0E-EC5F-4576-9DF7-AF68052E1152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{192F143D-BAEC-4662-86EC-0FD2BF508275}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{192F143D-BAEC-4662-86EC-0FD2BF508275}"/>
   </bookViews>
   <sheets>
     <sheet name="Condiciones Comerciales" sheetId="1" r:id="rId1"/>
@@ -1913,7 +1913,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1926,12 +1932,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -66837,28 +66837,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="Q1" s="155" t="s">
+      <c r="Q1" s="157" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="155"/>
-      <c r="S1" s="155"/>
-      <c r="T1" s="155"/>
-      <c r="U1" s="155"/>
-      <c r="V1" s="155"/>
-      <c r="W1" s="155"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="157"/>
+      <c r="W1" s="157"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="155"/>
-      <c r="R2" s="155"/>
-      <c r="S2" s="155"/>
-      <c r="T2" s="155"/>
-      <c r="U2" s="155"/>
-      <c r="V2" s="155"/>
-      <c r="W2" s="155"/>
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="157"/>
+      <c r="U2" s="157"/>
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
     </row>
     <row r="3" spans="1:29" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
@@ -66965,7 +66965,7 @@
         <v>22</v>
       </c>
       <c r="W4" s="152"/>
-      <c r="X4" s="156"/>
+      <c r="X4" s="158"/>
       <c r="AA4" s="29" t="s">
         <v>23</v>
       </c>
@@ -67973,20 +67973,20 @@
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B23" s="157" t="s">
+      <c r="B23" s="159" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="157"/>
-      <c r="D23" s="157"/>
-      <c r="E23" s="157"/>
-      <c r="F23" s="157"/>
-      <c r="G23" s="157"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="157"/>
-      <c r="K23" s="157"/>
-      <c r="L23" s="157"/>
-      <c r="M23" s="157"/>
+      <c r="C23" s="159"/>
+      <c r="D23" s="159"/>
+      <c r="E23" s="159"/>
+      <c r="F23" s="159"/>
+      <c r="G23" s="159"/>
+      <c r="H23" s="159"/>
+      <c r="I23" s="159"/>
+      <c r="J23" s="159"/>
+      <c r="K23" s="159"/>
+      <c r="L23" s="159"/>
+      <c r="M23" s="159"/>
       <c r="N23" s="71"/>
       <c r="R23" s="69" t="s">
         <v>106</v>
@@ -67996,20 +67996,20 @@
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B24" s="153" t="s">
+      <c r="B24" s="154" t="s">
         <v>108</v>
       </c>
-      <c r="C24" s="153"/>
-      <c r="D24" s="153"/>
-      <c r="E24" s="153"/>
-      <c r="F24" s="153"/>
-      <c r="G24" s="153"/>
-      <c r="H24" s="153"/>
-      <c r="I24" s="153"/>
-      <c r="J24" s="153"/>
-      <c r="K24" s="153"/>
-      <c r="L24" s="153"/>
-      <c r="M24" s="153"/>
+      <c r="C24" s="154"/>
+      <c r="D24" s="154"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="154"/>
+      <c r="G24" s="154"/>
+      <c r="H24" s="154"/>
+      <c r="I24" s="154"/>
+      <c r="J24" s="154"/>
+      <c r="K24" s="154"/>
+      <c r="L24" s="154"/>
+      <c r="M24" s="154"/>
       <c r="R24" s="70" t="s">
         <v>109</v>
       </c>
@@ -68018,38 +68018,38 @@
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B25" s="153" t="s">
+      <c r="B25" s="154" t="s">
         <v>111</v>
       </c>
-      <c r="C25" s="153"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
-      <c r="F25" s="153"/>
-      <c r="G25" s="153"/>
-      <c r="H25" s="153"/>
-      <c r="I25" s="153"/>
-      <c r="J25" s="153"/>
-      <c r="K25" s="153"/>
-      <c r="L25" s="153"/>
-      <c r="M25" s="153"/>
-      <c r="V25" s="154"/>
-      <c r="W25" s="154"/>
+      <c r="C25" s="154"/>
+      <c r="D25" s="154"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="154"/>
+      <c r="G25" s="154"/>
+      <c r="H25" s="154"/>
+      <c r="I25" s="154"/>
+      <c r="J25" s="154"/>
+      <c r="K25" s="154"/>
+      <c r="L25" s="154"/>
+      <c r="M25" s="154"/>
+      <c r="V25" s="156"/>
+      <c r="W25" s="156"/>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B26" s="153" t="s">
+      <c r="B26" s="154" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="153"/>
-      <c r="D26" s="153"/>
-      <c r="E26" s="153"/>
-      <c r="F26" s="153"/>
-      <c r="G26" s="153"/>
-      <c r="H26" s="153"/>
-      <c r="I26" s="153"/>
-      <c r="J26" s="153"/>
-      <c r="K26" s="153"/>
-      <c r="L26" s="153"/>
-      <c r="M26" s="153"/>
+      <c r="C26" s="154"/>
+      <c r="D26" s="154"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="154"/>
+      <c r="G26" s="154"/>
+      <c r="H26" s="154"/>
+      <c r="I26" s="154"/>
+      <c r="J26" s="154"/>
+      <c r="K26" s="154"/>
+      <c r="L26" s="154"/>
+      <c r="M26" s="154"/>
       <c r="N26" s="73"/>
       <c r="R26" s="69" t="s">
         <v>113</v>
@@ -68059,20 +68059,20 @@
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B27" s="153" t="s">
+      <c r="B27" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="153"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
-      <c r="F27" s="153"/>
-      <c r="G27" s="153"/>
-      <c r="H27" s="153"/>
-      <c r="I27" s="153"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="153"/>
-      <c r="L27" s="153"/>
-      <c r="M27" s="153"/>
+      <c r="C27" s="154"/>
+      <c r="D27" s="154"/>
+      <c r="E27" s="154"/>
+      <c r="F27" s="154"/>
+      <c r="G27" s="154"/>
+      <c r="H27" s="154"/>
+      <c r="I27" s="154"/>
+      <c r="J27" s="154"/>
+      <c r="K27" s="154"/>
+      <c r="L27" s="154"/>
+      <c r="M27" s="154"/>
       <c r="N27" s="73"/>
       <c r="R27" s="1" t="s">
         <v>116</v>
@@ -68082,20 +68082,20 @@
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B28" s="153" t="s">
+      <c r="B28" s="154" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="153"/>
-      <c r="D28" s="153"/>
-      <c r="E28" s="153"/>
-      <c r="F28" s="153"/>
-      <c r="G28" s="153"/>
-      <c r="H28" s="153"/>
-      <c r="I28" s="153"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="153"/>
-      <c r="L28" s="153"/>
-      <c r="M28" s="153"/>
+      <c r="C28" s="154"/>
+      <c r="D28" s="154"/>
+      <c r="E28" s="154"/>
+      <c r="F28" s="154"/>
+      <c r="G28" s="154"/>
+      <c r="H28" s="154"/>
+      <c r="I28" s="154"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="154"/>
+      <c r="L28" s="154"/>
+      <c r="M28" s="154"/>
       <c r="N28" s="73"/>
       <c r="R28" s="1" t="s">
         <v>119</v>
@@ -68105,20 +68105,20 @@
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B29" s="153" t="s">
+      <c r="B29" s="154" t="s">
         <v>121</v>
       </c>
-      <c r="C29" s="153"/>
-      <c r="D29" s="153"/>
-      <c r="E29" s="153"/>
-      <c r="F29" s="153"/>
-      <c r="G29" s="153"/>
-      <c r="H29" s="153"/>
-      <c r="I29" s="153"/>
-      <c r="J29" s="153"/>
-      <c r="K29" s="153"/>
-      <c r="L29" s="153"/>
-      <c r="M29" s="153"/>
+      <c r="C29" s="154"/>
+      <c r="D29" s="154"/>
+      <c r="E29" s="154"/>
+      <c r="F29" s="154"/>
+      <c r="G29" s="154"/>
+      <c r="H29" s="154"/>
+      <c r="I29" s="154"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="154"/>
+      <c r="L29" s="154"/>
+      <c r="M29" s="154"/>
       <c r="R29" s="1" t="s">
         <v>122</v>
       </c>
@@ -68127,20 +68127,20 @@
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B30" s="158" t="s">
+      <c r="B30" s="153" t="s">
         <v>124</v>
       </c>
-      <c r="C30" s="158"/>
-      <c r="D30" s="158"/>
-      <c r="E30" s="158"/>
-      <c r="F30" s="158"/>
-      <c r="G30" s="158"/>
-      <c r="H30" s="158"/>
-      <c r="I30" s="158"/>
-      <c r="J30" s="158"/>
-      <c r="K30" s="158"/>
-      <c r="L30" s="158"/>
-      <c r="M30" s="158"/>
+      <c r="C30" s="153"/>
+      <c r="D30" s="153"/>
+      <c r="E30" s="153"/>
+      <c r="F30" s="153"/>
+      <c r="G30" s="153"/>
+      <c r="H30" s="153"/>
+      <c r="I30" s="153"/>
+      <c r="J30" s="153"/>
+      <c r="K30" s="153"/>
+      <c r="L30" s="153"/>
+      <c r="M30" s="153"/>
       <c r="R30" s="1" t="s">
         <v>125</v>
       </c>
@@ -68149,20 +68149,20 @@
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B31" s="158" t="s">
+      <c r="B31" s="153" t="s">
         <v>127</v>
       </c>
-      <c r="C31" s="158"/>
-      <c r="D31" s="158"/>
-      <c r="E31" s="158"/>
-      <c r="F31" s="158"/>
-      <c r="G31" s="158"/>
-      <c r="H31" s="158"/>
-      <c r="I31" s="158"/>
-      <c r="J31" s="158"/>
-      <c r="K31" s="158"/>
-      <c r="L31" s="158"/>
-      <c r="M31" s="158"/>
+      <c r="C31" s="153"/>
+      <c r="D31" s="153"/>
+      <c r="E31" s="153"/>
+      <c r="F31" s="153"/>
+      <c r="G31" s="153"/>
+      <c r="H31" s="153"/>
+      <c r="I31" s="153"/>
+      <c r="J31" s="153"/>
+      <c r="K31" s="153"/>
+      <c r="L31" s="153"/>
+      <c r="M31" s="153"/>
       <c r="R31" s="70" t="s">
         <v>128</v>
       </c>
@@ -68171,36 +68171,36 @@
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="B32" s="158" t="s">
+      <c r="B32" s="153" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="158"/>
-      <c r="D32" s="158"/>
-      <c r="E32" s="158"/>
-      <c r="F32" s="158"/>
-      <c r="G32" s="158"/>
-      <c r="H32" s="158"/>
-      <c r="I32" s="158"/>
-      <c r="J32" s="158"/>
-      <c r="K32" s="158"/>
-      <c r="L32" s="158"/>
-      <c r="M32" s="158"/>
+      <c r="C32" s="153"/>
+      <c r="D32" s="153"/>
+      <c r="E32" s="153"/>
+      <c r="F32" s="153"/>
+      <c r="G32" s="153"/>
+      <c r="H32" s="153"/>
+      <c r="I32" s="153"/>
+      <c r="J32" s="153"/>
+      <c r="K32" s="153"/>
+      <c r="L32" s="153"/>
+      <c r="M32" s="153"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B33" s="153" t="s">
+      <c r="B33" s="154" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="153"/>
-      <c r="D33" s="153"/>
-      <c r="E33" s="153"/>
-      <c r="F33" s="153"/>
-      <c r="G33" s="153"/>
-      <c r="H33" s="153"/>
-      <c r="I33" s="153"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="153"/>
-      <c r="L33" s="153"/>
-      <c r="M33" s="153"/>
+      <c r="C33" s="154"/>
+      <c r="D33" s="154"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="154"/>
+      <c r="G33" s="154"/>
+      <c r="H33" s="154"/>
+      <c r="I33" s="154"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="154"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="154"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="74"/>
@@ -68282,9 +68282,9 @@
       <c r="B42" s="69"/>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B43" s="159"/>
-      <c r="C43" s="159"/>
-      <c r="D43" s="159"/>
+      <c r="B43" s="155"/>
+      <c r="C43" s="155"/>
+      <c r="D43" s="155"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:M21" xr:uid="{27C47C64-5BA2-4774-BE4B-59B66BC9B742}">
@@ -68311,6 +68311,13 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="16">
+    <mergeCell ref="B25:M25"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="Q1:W2"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="V4:X4"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="B24:M24"/>
     <mergeCell ref="B32:M32"/>
     <mergeCell ref="B33:M33"/>
     <mergeCell ref="B43:D43"/>
@@ -68320,13 +68327,6 @@
     <mergeCell ref="B29:M29"/>
     <mergeCell ref="B30:M30"/>
     <mergeCell ref="B31:M31"/>
-    <mergeCell ref="B25:M25"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="Q1:W2"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="B24:M24"/>
   </mergeCells>
   <conditionalFormatting sqref="T4 X4 T6:T17 X6:X19">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="VB">
@@ -68398,11 +68398,11 @@
     <row r="7" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="25"/>
       <c r="C7" s="80" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D7" s="81" t="str">
         <f>VLOOKUP(C7,'Condiciones Comerciales'!$B$3:$C$21,2,FALSE)</f>
-        <v>Pre-entrega</v>
+        <v>Inmediata</v>
       </c>
       <c r="H7" s="31"/>
     </row>
@@ -68424,7 +68424,7 @@
         <v>138</v>
       </c>
       <c r="D10" s="83">
-        <v>3319</v>
+        <v>2519</v>
       </c>
       <c r="H10" s="31"/>
     </row>
@@ -68434,7 +68434,7 @@
         <v>139</v>
       </c>
       <c r="D11" s="83">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="F11" s="69"/>
       <c r="G11" s="84"/>
@@ -68447,7 +68447,7 @@
         <v>140</v>
       </c>
       <c r="D12" s="83">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F12" s="86"/>
       <c r="G12" s="87"/>
@@ -68457,7 +68457,7 @@
       <c r="B13" s="25"/>
       <c r="D13" s="89">
         <f>SUM(D10:D12)</f>
-        <v>3749</v>
+        <v>2519</v>
       </c>
       <c r="F13" s="86"/>
       <c r="G13" s="87"/>
@@ -68503,7 +68503,7 @@
       </c>
       <c r="D18" s="139">
         <f>D10*(100%-D15)</f>
-        <v>2887.53</v>
+        <v>2191.5300000000002</v>
       </c>
       <c r="H18" s="31"/>
     </row>
@@ -68514,7 +68514,7 @@
       </c>
       <c r="D19" s="139">
         <f>D11</f>
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="F19" s="69"/>
       <c r="G19" s="84"/>
@@ -68528,7 +68528,7 @@
       </c>
       <c r="D20" s="139">
         <f>D12</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F20" s="86"/>
       <c r="G20" s="92"/>
@@ -68541,7 +68541,7 @@
       </c>
       <c r="D21" s="141">
         <f>SUM(D18:D20)</f>
-        <v>3317.53</v>
+        <v>2191.5300000000002</v>
       </c>
       <c r="F21" s="86"/>
       <c r="G21" s="92"/>
@@ -68588,7 +68588,7 @@
       </c>
       <c r="E25" s="98">
         <f>D25/$D$21</f>
-        <v>7.573218097334354E-4</v>
+        <v>1.1464309516387929E-3</v>
       </c>
       <c r="F25" s="99"/>
       <c r="G25" s="99"/>
@@ -68614,7 +68614,7 @@
       </c>
       <c r="D27" s="147">
         <f>D21*D26</f>
-        <v>66.3506</v>
+        <v>43.830600000000004</v>
       </c>
       <c r="E27" s="98">
         <f>D27/$D$21</f>
@@ -68631,23 +68631,23 @@
       </c>
       <c r="D28" s="147">
         <f>IF(D23=0%,0,D21*D23-D25-D27)</f>
-        <v>262.88996217655512</v>
+        <v>172.80996217655505</v>
       </c>
       <c r="E28" s="98">
         <f>D28/$D$21</f>
-        <v>7.9242678190266577E-2</v>
+        <v>7.8853569048361202E-2</v>
       </c>
       <c r="F28" s="102" t="str">
         <f>IF(D7="Inmediata","* Mutuo Maestra 60 cuotas de:", "* Cuotas sin interés desde:")</f>
-        <v>* Cuotas sin interés desde:</v>
+        <v>* Mutuo Maestra 60 cuotas de:</v>
       </c>
       <c r="G28" s="103">
         <f>IF(D7="Inmediata",-PMT(5%/12,60,D28),7)</f>
-        <v>7</v>
+        <v>3.261137172246463</v>
       </c>
       <c r="H28" s="104">
         <f>+G28*H23</f>
-        <v>278613.86000000004</v>
+        <v>129799.71650701029</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -68657,19 +68657,19 @@
       </c>
       <c r="D29" s="101">
         <f>+D21*(100%-D23)</f>
-        <v>2985.777</v>
+        <v>1972.3770000000002</v>
       </c>
       <c r="E29" s="98">
         <f>D29/$D$21</f>
-        <v>0.89999999999999991</v>
+        <v>0.9</v>
       </c>
       <c r="F29" s="102" t="str">
         <f>IF(G28=7,"Cuotas de UF 7:","")</f>
-        <v>Cuotas de UF 7:</v>
-      </c>
-      <c r="G29" s="105">
+        <v/>
+      </c>
+      <c r="G29" s="105" t="str">
         <f>IF(G28=7,ROUNDDOWN(D28/7,0),"")</f>
-        <v>37</v>
+        <v/>
       </c>
       <c r="H29" s="106"/>
     </row>
@@ -68679,11 +68679,11 @@
       <c r="E30" s="107"/>
       <c r="F30" s="102" t="str">
         <f>IF(G28=7,"Diferencia cuota adicional:","")</f>
-        <v>Diferencia cuota adicional:</v>
-      </c>
-      <c r="G30" s="103">
+        <v/>
+      </c>
+      <c r="G30" s="103" t="str">
         <f>IF(G28=7,D28-(G28*G29),"")</f>
-        <v>3.889962176555116</v>
+        <v/>
       </c>
       <c r="H30" s="100"/>
     </row>
@@ -68697,15 +68697,15 @@
       </c>
       <c r="F31" s="108" t="str">
         <f>IF(G28=7,"Máximo de cuotas Proyecto:","")</f>
-        <v>Máximo de cuotas Proyecto:</v>
-      </c>
-      <c r="G31" s="109">
+        <v/>
+      </c>
+      <c r="G31" s="109" t="str">
         <f>IF(G28=7,VLOOKUP(C7,'Condiciones Comerciales'!B3:J21,9,FALSE),"")</f>
-        <v>60</v>
+        <v/>
       </c>
       <c r="H31" s="110" t="str">
         <f>IF(G28=7,IF(G31&gt;=(G29+1),"OK","No Cumple"),"")</f>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="32" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -68749,7 +68749,7 @@
       </c>
       <c r="D35" s="150">
         <f>D29/D33</f>
-        <v>3732.2212500000001</v>
+        <v>2465.4712500000001</v>
       </c>
       <c r="H35" s="31"/>
     </row>
@@ -68760,11 +68760,11 @@
       </c>
       <c r="D36" s="135">
         <f>D35-D37-D38</f>
-        <v>414.69124999999985</v>
+        <v>273.94125000000008</v>
       </c>
       <c r="E36" s="136">
         <f>D36/$D$35</f>
-        <v>0.11111111111111108</v>
+        <v>0.11111111111111115</v>
       </c>
       <c r="H36" s="31"/>
     </row>
@@ -68775,11 +68775,11 @@
       </c>
       <c r="D37" s="150">
         <f>D25+D27+D28</f>
-        <v>331.7530000000001</v>
+        <v>219.15300000000002</v>
       </c>
       <c r="E37" s="151">
         <f t="shared" ref="E37:E38" si="0">D37/$D$35</f>
-        <v>8.888888888888892E-2</v>
+        <v>8.8888888888888892E-2</v>
       </c>
       <c r="H37" s="31"/>
     </row>
@@ -68790,7 +68790,7 @@
       </c>
       <c r="D38" s="150">
         <f>D35*D33</f>
-        <v>2985.777</v>
+        <v>1972.3770000000002</v>
       </c>
       <c r="E38" s="151">
         <f t="shared" si="0"/>
@@ -68801,11 +68801,11 @@
       </c>
       <c r="G38" s="115">
         <f>PMT(4%/12,300,-D38)</f>
-        <v>15.760030975137768</v>
+        <v>10.410932435560092</v>
       </c>
       <c r="H38" s="116">
         <f>+G38*H23</f>
-        <v>627280.437671814</v>
+        <v>414375.72458151408</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -68880,7 +68880,7 @@
       <c r="G44" s="115"/>
       <c r="H44" s="126">
         <f>+D43/24+D44-G38</f>
-        <v>-5.3752879715652497</v>
+        <v>-2.6189431987573286E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -68892,7 +68892,7 @@
       <c r="G45" s="65"/>
       <c r="H45" s="127">
         <f>+H44*H23</f>
-        <v>-213947.10433848065</v>
+        <v>-1042.3912481807522</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
